--- a/MA_TRAN_THUC_NGHIEM_SKQ_FULL.xlsx
+++ b/MA_TRAN_THUC_NGHIEM_SKQ_FULL.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Ma_tran" sheetId="1" r:id="Re51e95ed75324bfa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Tai_lieu" sheetId="2" r:id="R41ed3af6778a446c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Input_Output" sheetId="3" r:id="R656f55b435d2490f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Model_Config" sheetId="4" r:id="Rea62404bcf8c447d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Compression_Config" sheetId="5" r:id="R5d47dd5dcfb746df"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Metrics" sheetId="6" r:id="R5f18925ae62a4a0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Ma_tran" sheetId="1" r:id="R51b80f3f0c3746e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Tai_lieu" sheetId="2" r:id="R63b29821e6724230"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Input_Output" sheetId="3" r:id="R7a6d1a4c32e345d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Model_Config" sheetId="4" r:id="Rd22026ce66ef4c54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Compression_Config" sheetId="5" r:id="R6d8ab09563434d37"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_Metrics" sheetId="6" r:id="R7c93c31cfb584b9c"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1134,12 +1134,6 @@
     <x:t xml:space="preserve">X_train; y_train; row_id; method config; budget hoặc native-size policy; selector seed.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Chạy N01/N02, BDIS, AutoCoreset, CRAIG, G-Coreset/Leverage hoặc SKQ. Selector không được nhìn test.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">selected_indices; sample_weights; realized_size; realized_ratio; structure artifact nếu phương pháp có vùng/leaf.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">artifacts/selections/{dataset}/{method}/{run_id}/</x:t>
   </x:si>
   <x:si>
@@ -2911,9 +2905,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Per-example/full gradients</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">CRAIG/gradient methods</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Method-specific</x:t>
@@ -3615,7 +3606,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="79">
+  <x:cellXfs count="85">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3849,6 +3840,24 @@
     <x:xf numFmtId="0" fontId="15" fillId="10" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="16" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -4062,6 +4071,7 @@
     <x:col min="6" max="6" width="13" customWidth="1"/>
     <x:col min="7" max="11" width="7" customWidth="1"/>
     <x:col min="12" max="12" width="42" customWidth="1"/>
+    <x:col min="13" max="13" width="41.25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
@@ -4082,7 +4092,7 @@
     </x:row>
     <x:row r="2" ht="26" customHeight="1">
       <x:c r="A2" s="51" t="str">
-        <x:v>Cấu hình full-v3 có 26 phương pháp × 5 downstream learner = 130 ô ở mỗi seed; các biến thể P chỉ được chọn winner trên dev.</x:v>
+        <x:v>Cấu hình full-v4 có 28 phương pháp × 5 downstream learner = 140 ô ở mỗi seed; P10/P11 là biến thể scale-out mới và chưa có metric Adult trước lần chạy v4.</x:v>
       </x:c>
       <x:c r="B2" s="51"/>
       <x:c r="C2" s="51"/>
@@ -4163,6 +4173,9 @@
       <x:c r="L5" s="1" t="s">
         <x:v>12</x:v>
       </x:c>
+      <x:c r="M5" s="79" t="str">
+        <x:v>Ưu / nhược trên dữ liệu nhỏ (Adult)</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="36" customHeight="1">
       <x:c r="A6" s="3">
@@ -4201,6 +4214,9 @@
       <x:c r="L6" s="2" t="s">
         <x:v>19</x:v>
       </x:c>
+      <x:c r="M6" s="72" t="str">
+        <x:v>Ưu: trần utility, F1_macro TB 0,7874. Nhược: dùng 27.676 dòng (100%), không nén.</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="36" customHeight="1">
       <x:c r="A7" s="3">
@@ -4239,6 +4255,9 @@
       <x:c r="L7" s="2" t="str">
         <x:v>full-v2/v3 integration chạy đủ 5 learner; confirmatory vẫn có thể khóa riêng theo protocol.</x:v>
       </x:c>
+      <x:c r="M7" s="72" t="str">
+        <x:v>Ưu: cực nhanh (~0,002 s), F1 0,7709. Nhược: không khai thác cấu trúc dữ liệu.</x:v>
+      </x:c>
     </x:row>
     <x:row r="8" ht="36" customHeight="1">
       <x:c r="A8" s="7">
@@ -4277,6 +4296,9 @@
       <x:c r="L8" s="2" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="M8" s="72" t="str">
+        <x:v>Ưu: source chính thức, ~2,59 s. Nhược: 4.485 dòng nhưng F1 thấp 0,6231 trên Adult.</x:v>
+      </x:c>
     </x:row>
     <x:row r="9" ht="36" customHeight="1">
       <x:c r="A9" s="7">
@@ -4315,6 +4337,9 @@
       <x:c r="L9" s="2" t="s">
         <x:v>29</x:v>
       </x:c>
+      <x:c r="M9" s="72" t="str">
+        <x:v>Ưu: F1 0,7782 và ~1,99 s. Nhược: giữ 17.209 dòng (~62%), nén yếu trên Adult nhỏ.</x:v>
+      </x:c>
     </x:row>
     <x:row r="10" ht="36" customHeight="1">
       <x:c r="A10" s="7">
@@ -4353,6 +4378,9 @@
       <x:c r="L10" s="2" t="s">
         <x:v>37</x:v>
       </x:c>
+      <x:c r="M10" s="72" t="str">
+        <x:v>Ưu: F1 0,7787, chỉ 1.083 dòng và ~4,46 s. Nhược: size native không khớp đúng 5%.</x:v>
+      </x:c>
     </x:row>
     <x:row r="11" ht="36" customHeight="1">
       <x:c r="A11" s="7">
@@ -4391,6 +4419,9 @@
       <x:c r="L11" s="2" t="s">
         <x:v>41</x:v>
       </x:c>
+      <x:c r="M11" s="72" t="str">
+        <x:v>Ưu: 750 dòng. Nhược: F1 0,7367 và ~12,92 s; thấp hơn nhiều baseline 5%.</x:v>
+      </x:c>
     </x:row>
     <x:row r="12" ht="36" customHeight="1">
       <x:c r="A12" s="7">
@@ -4429,6 +4460,9 @@
       <x:c r="L12" s="2" t="str">
         <x:v>Adaptation R1 để so sánh; không claim native CRAIG và không thay bằng CORDS.</x:v>
       </x:c>
+      <x:c r="M12" s="72" t="str">
+        <x:v>Ưu: exact ~5%, F1 0,7663. Nhược: chậm nhất trong nhóm real-row nền (~51,43 s).</x:v>
+      </x:c>
     </x:row>
     <x:row r="13" ht="36" customHeight="1">
       <x:c r="A13" s="7" t="n">
@@ -4467,6 +4501,9 @@
       <x:c r="L13" s="2" t="str">
         <x:v>Gọi trực tiếp function upstream đã khóa commit; không gộp hai thuật toán trong bảng kết quả</x:v>
       </x:c>
+      <x:c r="M13" s="72" t="str">
+        <x:v>Gonzalez: F1 0,7776 nhưng ~12,34 s; Leverage: rất nhanh ~0,039 s nhưng F1 0,7683.</x:v>
+      </x:c>
     </x:row>
     <x:row r="14" ht="36" customHeight="1">
       <x:c r="A14" s="9">
@@ -4505,6 +4542,9 @@
       <x:c r="L14" s="2" t="s">
         <x:v>19</x:v>
       </x:c>
+      <x:c r="M14" s="72" t="str">
+        <x:v>Ưu: kiểm tra đóng góp herding. Nhược: F1 0,7680, không hơn random rõ trên Adult.</x:v>
+      </x:c>
     </x:row>
     <x:row r="15" ht="36" customHeight="1">
       <x:c r="A15" s="9">
@@ -4543,6 +4583,9 @@
       <x:c r="L15" s="2" t="s">
         <x:v>49</x:v>
       </x:c>
+      <x:c r="M15" s="72" t="str">
+        <x:v>Ưu: ~2,43 s, exact 5%. Nhược: F1 0,7674; bỏ structure làm giảm utility.</x:v>
+      </x:c>
     </x:row>
     <x:row r="16" ht="36" customHeight="1">
       <x:c r="A16" s="9">
@@ -4581,6 +4624,9 @@
       <x:c r="L16" s="2" t="s">
         <x:v>19</x:v>
       </x:c>
+      <x:c r="M16" s="72" t="str">
+        <x:v>Ưu: ablation rõ vai trò QP. Nhược: F1 0,7648 và timing kế thừa source ~25,14 s.</x:v>
+      </x:c>
     </x:row>
     <x:row r="17" ht="36" customHeight="1">
       <x:c r="A17" s="11" t="n">
@@ -4619,6 +4665,9 @@
       <x:c r="L17" s="2" t="str">
         <x:v>Synthetic baselines qua adapter đã khai báo patch/profile. Chỉ ghi SUCCESS khi chạy thật; OOM/TIMEOUT/BLOCKED vẫn giữ trong mẫu số.</x:v>
       </x:c>
+      <x:c r="M17" s="72" t="str">
+        <x:v>Ưu: đủ 5 synthetic đều chạy. Nhược: F1 dao động 0,3977–0,7324, dưới real-row mạnh; có patch/profile.</x:v>
+      </x:c>
     </x:row>
     <x:row r="18" ht="36" customHeight="1">
       <x:c r="A18" s="14">
@@ -4657,6 +4706,9 @@
       <x:c r="L18" s="2" t="str">
         <x:v>P01/P02 exact 5%; P03 target 5% nhưng realized=min(target, BDIS pool). Báo cáo requested + realized size; pool nhỏ không là resource failure. Chọn base winner trên dev rồi cố định.</x:v>
       </x:c>
+      <x:c r="M18" s="72" t="str">
+        <x:v>P01/P02/P03: F1 lần lượt 0,7509/0,7655/0,7649; P03 chỉ 1.083 dòng. Chưa thắng BDIS native.</x:v>
+      </x:c>
     </x:row>
     <x:row r="19" ht="36" customHeight="1">
       <x:c r="A19" s="14">
@@ -4695,6 +4747,9 @@
       <x:c r="L19" s="2" t="str">
         <x:v>s1_screen: chạy dev trước freeze, confirmatory_eligible=false; s2_confirm/test cần freeze manifest.</x:v>
       </x:c>
+      <x:c r="M19" s="72" t="str">
+        <x:v>Ưu: query một learner, exact 5%. Nhược: F1 0,7638, ~8,52 s; chưa có lợi trên Adult.</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" ht="36" customHeight="1">
       <x:c r="A20" s="14">
@@ -4732,6 +4787,9 @@
       </x:c>
       <x:c r="L20" s="2" t="str">
         <x:v>s1_screen: chạy dev trước freeze; s2_confirm/test cần freeze; chỉ giữ nếu lợi ích xứng đáng chi phí.</x:v>
+      </x:c>
+      <x:c r="M20" s="72" t="str">
+        <x:v>Ưu: query đa learner. Nhược: F1 0,7645, ~25,08 s; chi phí tăng nhưng utility không tăng.</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -4749,6 +4807,7 @@
       <x:c r="J21" s="54"/>
       <x:c r="K21" s="54"/>
       <x:c r="L21" s="55"/>
+      <x:c r="M21" s="80"/>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="56" t="s">
@@ -4769,6 +4828,7 @@
       <x:c r="J22" s="56"/>
       <x:c r="K22" s="56"/>
       <x:c r="L22" s="56"/>
+      <x:c r="M22" s="80"/>
     </x:row>
     <x:row r="23" ht="34" customHeight="1">
       <x:c r="A23" s="57" t="s">
@@ -4789,6 +4849,7 @@
       <x:c r="J23" s="59"/>
       <x:c r="K23" s="59"/>
       <x:c r="L23" s="60"/>
+      <x:c r="M23" s="80"/>
     </x:row>
     <x:row r="24" ht="34" customHeight="1">
       <x:c r="A24" s="57" t="s">
@@ -4809,6 +4870,7 @@
       <x:c r="J24" s="59"/>
       <x:c r="K24" s="59"/>
       <x:c r="L24" s="60"/>
+      <x:c r="M24" s="80"/>
     </x:row>
     <x:row r="25" ht="34" customHeight="1">
       <x:c r="A25" s="57" t="str">
@@ -4829,6 +4891,7 @@
       <x:c r="J25" s="59"/>
       <x:c r="K25" s="59"/>
       <x:c r="L25" s="60"/>
+      <x:c r="M25" s="80"/>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="16"/>
@@ -4843,6 +4906,7 @@
       <x:c r="J26" s="16"/>
       <x:c r="K26" s="16"/>
       <x:c r="L26" s="16"/>
+      <x:c r="M26" s="80"/>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="53" t="s">
@@ -4859,6 +4923,7 @@
       <x:c r="J27" s="54"/>
       <x:c r="K27" s="54"/>
       <x:c r="L27" s="55"/>
+      <x:c r="M27" s="80"/>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="56" t="s">
@@ -4879,6 +4944,7 @@
       <x:c r="J28" s="56"/>
       <x:c r="K28" s="56"/>
       <x:c r="L28" s="56"/>
+      <x:c r="M28" s="80"/>
     </x:row>
     <x:row r="29" ht="33" customHeight="1">
       <x:c r="A29" s="61">
@@ -4899,6 +4965,7 @@
       <x:c r="J29" s="59"/>
       <x:c r="K29" s="59"/>
       <x:c r="L29" s="60"/>
+      <x:c r="M29" s="80"/>
     </x:row>
     <x:row r="30" ht="33" customHeight="1">
       <x:c r="A30" s="61">
@@ -4919,6 +4986,7 @@
       <x:c r="J30" s="59"/>
       <x:c r="K30" s="59"/>
       <x:c r="L30" s="60"/>
+      <x:c r="M30" s="80"/>
     </x:row>
     <x:row r="31" ht="33" customHeight="1">
       <x:c r="A31" s="61">
@@ -4939,6 +5007,7 @@
       <x:c r="J31" s="59"/>
       <x:c r="K31" s="59"/>
       <x:c r="L31" s="60"/>
+      <x:c r="M31" s="80"/>
     </x:row>
     <x:row r="32" ht="33" customHeight="1">
       <x:c r="A32" s="61">
@@ -4959,6 +5028,7 @@
       <x:c r="J32" s="59"/>
       <x:c r="K32" s="59"/>
       <x:c r="L32" s="60"/>
+      <x:c r="M32" s="80"/>
     </x:row>
     <x:row r="33" ht="33" customHeight="1">
       <x:c r="A33" s="61">
@@ -4979,6 +5049,7 @@
       <x:c r="J33" s="59"/>
       <x:c r="K33" s="59"/>
       <x:c r="L33" s="60"/>
+      <x:c r="M33" s="80"/>
     </x:row>
     <x:row r="34" ht="33" customHeight="1">
       <x:c r="A34" s="61">
@@ -4999,6 +5070,7 @@
       <x:c r="J34" s="59"/>
       <x:c r="K34" s="59"/>
       <x:c r="L34" s="60"/>
+      <x:c r="M34" s="80"/>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="16"/>
@@ -5013,6 +5085,7 @@
       <x:c r="J35" s="16"/>
       <x:c r="K35" s="16"/>
       <x:c r="L35" s="16"/>
+      <x:c r="M35" s="80"/>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="53" t="s">
@@ -5029,6 +5102,7 @@
       <x:c r="J36" s="54"/>
       <x:c r="K36" s="54"/>
       <x:c r="L36" s="55"/>
+      <x:c r="M36" s="80"/>
     </x:row>
     <x:row r="37" ht="30" customHeight="1">
       <x:c r="A37" s="57" t="s">
@@ -5051,6 +5125,7 @@
       <x:c r="J37" s="59"/>
       <x:c r="K37" s="59"/>
       <x:c r="L37" s="60"/>
+      <x:c r="M37" s="80"/>
     </x:row>
     <x:row r="38" ht="30" customHeight="1">
       <x:c r="A38" s="57" t="s">
@@ -5073,6 +5148,7 @@
       <x:c r="J38" s="59"/>
       <x:c r="K38" s="59"/>
       <x:c r="L38" s="60"/>
+      <x:c r="M38" s="80"/>
     </x:row>
     <x:row r="39" ht="30" customHeight="1">
       <x:c r="A39" s="57" t="s">
@@ -5095,6 +5171,7 @@
       <x:c r="J39" s="59"/>
       <x:c r="K39" s="59"/>
       <x:c r="L39" s="60"/>
+      <x:c r="M39" s="80"/>
     </x:row>
     <x:row r="40" ht="30" customHeight="1">
       <x:c r="A40" s="57" t="s">
@@ -5117,6 +5194,7 @@
       <x:c r="J40" s="59"/>
       <x:c r="K40" s="59"/>
       <x:c r="L40" s="60"/>
+      <x:c r="M40" s="80"/>
     </x:row>
     <x:row r="41" ht="30" customHeight="1">
       <x:c r="A41" s="57" t="s">
@@ -5139,6 +5217,7 @@
       <x:c r="J41" s="59"/>
       <x:c r="K41" s="59"/>
       <x:c r="L41" s="60"/>
+      <x:c r="M41" s="80"/>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="16"/>
@@ -5153,6 +5232,7 @@
       <x:c r="J42" s="16"/>
       <x:c r="K42" s="16"/>
       <x:c r="L42" s="16"/>
+      <x:c r="M42" s="80"/>
     </x:row>
     <x:row r="43" ht="28" customHeight="1">
       <x:c r="A43" s="63" t="s">
@@ -5169,10 +5249,11 @@
       <x:c r="J43" s="63"/>
       <x:c r="K43" s="63"/>
       <x:c r="L43" s="63"/>
+      <x:c r="M43" s="80"/>
     </x:row>
     <x:row r="44" ht="24" customHeight="1">
       <x:c r="A44" s="53" t="str">
-        <x:v>BIẾN THỂ ĐỀ XUẤT – PROTOCOL V3 (DEV SCREEN)</x:v>
+        <x:v>BIẾN THỂ ĐỀ XUẤT – PROTOCOL V4 (DEV SCREEN)</x:v>
       </x:c>
       <x:c r="B44" s="54"/>
       <x:c r="C44" s="54"/>
@@ -5185,6 +5266,7 @@
       <x:c r="J44" s="54"/>
       <x:c r="K44" s="54"/>
       <x:c r="L44" s="55"/>
+      <x:c r="M44" s="80"/>
     </x:row>
     <x:row r="45" ht="42" customHeight="1">
       <x:c r="A45" s="69" t="n">
@@ -5223,6 +5305,9 @@
       <x:c r="L45" s="72" t="str">
         <x:v>P06 giữ nguyên index Gonzalez 1×; chỉ là dev screen, chưa phải winner.</x:v>
       </x:c>
+      <x:c r="M45" s="72" t="str">
+        <x:v>Ưu: F1 0,7786, cùng index Gonzalez nên cô lập QP. Nhược: ~14,83 s.</x:v>
+      </x:c>
     </x:row>
     <x:row r="46" ht="42" customHeight="1">
       <x:c r="A46" s="69" t="n">
@@ -5261,6 +5346,9 @@
       <x:c r="L46" s="72" t="str">
         <x:v>Pool 2× là artifact trung gian; output cuối đúng 5%.</x:v>
       </x:c>
+      <x:c r="M46" s="72" t="str">
+        <x:v>Ưu: coverage pool 2× rồi exact 5%. Nhược: F1 0,7689 và ~31,79 s.</x:v>
+      </x:c>
     </x:row>
     <x:row r="47" ht="42" customHeight="1">
       <x:c r="A47" s="69" t="n">
@@ -5299,6 +5387,9 @@
       <x:c r="L47" s="72" t="str">
         <x:v>s1/dev screen được chạy; confirmatory/test cần freeze parent Gonzalez phù hợp.</x:v>
       </x:c>
+      <x:c r="M47" s="72" t="str">
+        <x:v>Ưu: proposed tốt nhất Adult hiện tại, F1 0,7794. Nhược: ~38,90 s; chỉ hơn P06 rất ít.</x:v>
+      </x:c>
     </x:row>
     <x:row r="48" ht="42" customHeight="1">
       <x:c r="A48" s="69" t="n">
@@ -5337,10 +5428,94 @@
       <x:c r="L48" s="72" t="str">
         <x:v>s1/dev screen được chạy; không đổi portfolio sau khi xem test.</x:v>
       </x:c>
+      <x:c r="M48" s="72" t="str">
+        <x:v>Ưu: F1 0,7777. Nhược: chậm ~54,19 s; MQ không hơn SQ trên Adult.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A49" s="69" t="n">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B49" s="69" t="str">
+        <x:v>P10</x:v>
+      </x:c>
+      <x:c r="C49" s="70" t="str">
+        <x:v>Đề xuất</x:v>
+      </x:c>
+      <x:c r="D49" s="70" t="str">
+        <x:v>SKQ-MR-CoreTab-XGB</x:v>
+      </x:c>
+      <x:c r="E49" s="70" t="str">
+        <x:v>CoreTab-XGB theo shard; gộp leaf nhỏ; SKQ streaming cấp budget toàn cục.</x:v>
+      </x:c>
+      <x:c r="F49" s="69" t="str">
+        <x:v>5%</x:v>
+      </x:c>
+      <x:c r="G49" s="71" t="str">
+        <x:v>✓</x:v>
+      </x:c>
+      <x:c r="H49" s="71" t="str">
+        <x:v>✓</x:v>
+      </x:c>
+      <x:c r="I49" s="71" t="str">
+        <x:v>✓</x:v>
+      </x:c>
+      <x:c r="J49" s="71" t="str">
+        <x:v>✓</x:v>
+      </x:c>
+      <x:c r="K49" s="71" t="str">
+        <x:v>✓</x:v>
+      </x:c>
+      <x:c r="L49" s="72" t="str">
+        <x:v>Đề xuất scale-out; đọc đủ train, không proxy; exact budget; không phải CoreTab native nguyên trạng.</x:v>
+      </x:c>
+      <x:c r="M49" s="72" t="str">
+        <x:v>Chưa chạy Adult v4. Kỳ vọng giảm đỉnh RAM; trên data nhỏ có overhead nhiều shard nên có thể không nhanh hơn P02/P06.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="A50" s="69" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B50" s="69" t="str">
+        <x:v>P11</x:v>
+      </x:c>
+      <x:c r="C50" s="70" t="str">
+        <x:v>Đề xuất</x:v>
+      </x:c>
+      <x:c r="D50" s="70" t="str">
+        <x:v>SKQ-MR-BDIS</x:v>
+      </x:c>
+      <x:c r="E50" s="70" t="str">
+        <x:v>BDIS theo shard tạo candidate; SKQ streaming reduce toàn cục.</x:v>
+      </x:c>
+      <x:c r="F50" s="69" t="str">
+        <x:v>≤5%</x:v>
+      </x:c>
+      <x:c r="G50" s="71" t="str">
+        <x:v>✓</x:v>
+      </x:c>
+      <x:c r="H50" s="71" t="str">
+        <x:v>✓</x:v>
+      </x:c>
+      <x:c r="I50" s="71" t="str">
+        <x:v>✓</x:v>
+      </x:c>
+      <x:c r="J50" s="71" t="str">
+        <x:v>✓</x:v>
+      </x:c>
+      <x:c r="K50" s="71" t="str">
+        <x:v>✓</x:v>
+      </x:c>
+      <x:c r="L50" s="72" t="str">
+        <x:v>Đề xuất scale-out; đọc đủ train, không proxy; cap theo candidate BDIS, không pad/trùng.</x:v>
+      </x:c>
+      <x:c r="M50" s="72" t="str">
+        <x:v>Chưa chạy Adult v4. Có thể giữ ưu thế BDIS; nhược là realized size phụ thuộc tổng candidate từng shard.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="A43:L43"/>
     <x:mergeCell ref="A40:B40"/>
     <x:mergeCell ref="C40:F40"/>
     <x:mergeCell ref="G40:H40"/>
@@ -5357,7 +5532,6 @@
     <x:mergeCell ref="C39:F39"/>
     <x:mergeCell ref="G39:H39"/>
     <x:mergeCell ref="I39:L39"/>
-    <x:mergeCell ref="A36:L36"/>
     <x:mergeCell ref="A37:B37"/>
     <x:mergeCell ref="C37:F37"/>
     <x:mergeCell ref="G37:H37"/>
@@ -5383,7 +5557,6 @@
     <x:mergeCell ref="A25:B25"/>
     <x:mergeCell ref="C25:F25"/>
     <x:mergeCell ref="G25:L25"/>
-    <x:mergeCell ref="A27:L27"/>
     <x:mergeCell ref="A28:B28"/>
     <x:mergeCell ref="C28:E28"/>
     <x:mergeCell ref="F28:L28"/>
@@ -5393,14 +5566,17 @@
     <x:mergeCell ref="A24:B24"/>
     <x:mergeCell ref="C24:F24"/>
     <x:mergeCell ref="G24:L24"/>
-    <x:mergeCell ref="A1:L1"/>
-    <x:mergeCell ref="A2:L2"/>
-    <x:mergeCell ref="A3:L3"/>
-    <x:mergeCell ref="A21:L21"/>
     <x:mergeCell ref="A22:B22"/>
     <x:mergeCell ref="C22:F22"/>
     <x:mergeCell ref="G22:L22"/>
-    <x:mergeCell ref="A44:L44"/>
+    <x:mergeCell ref="A1:M1"/>
+    <x:mergeCell ref="A2:M2"/>
+    <x:mergeCell ref="A3:M3"/>
+    <x:mergeCell ref="A21:M21"/>
+    <x:mergeCell ref="A27:M27"/>
+    <x:mergeCell ref="A36:M36"/>
+    <x:mergeCell ref="A43:M43"/>
+    <x:mergeCell ref="A44:M44"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -6602,20 +6778,20 @@
       <x:c r="C8" s="30" t="s">
         <x:v>324</x:v>
       </x:c>
-      <x:c r="D8" s="30" t="s">
+      <x:c r="D8" s="30" t="str">
+        <x:v>Chạy N01/N02, BDIS, AutoCoreset, CRAIG, G-Coreset/Leverage hoặc SKQ. Với P10/P11, chia shard xác định nhưng mọi dòng train vẫn được đọc đúng một lần; không dùng proxy. Selector không được nhìn test.</x:v>
+      </x:c>
+      <x:c r="E8" s="30" t="str">
+        <x:v>selected_indices; sample_weights; realized_size/ratio; structure artifact; với P10/P11 thêm shard_count, largest_shard_rows, all_train_rows_seen và proxy_dataset=false.</x:v>
+      </x:c>
+      <x:c r="F8" s="33" t="s">
         <x:v>325</x:v>
       </x:c>
-      <x:c r="E8" s="30" t="s">
+      <x:c r="G8" s="30" t="s">
         <x:v>326</x:v>
       </x:c>
-      <x:c r="F8" s="33" t="s">
+      <x:c r="H8" s="30" t="s">
         <x:v>327</x:v>
-      </x:c>
-      <x:c r="G8" s="30" t="s">
-        <x:v>328</x:v>
-      </x:c>
-      <x:c r="H8" s="30" t="s">
-        <x:v>329</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="88" customHeight="1">
@@ -6623,25 +6799,25 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="37" t="s">
-        <x:v>330</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="C9" s="30" t="s">
-        <x:v>331</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D9" s="30" t="str">
         <x:v>Chạy KIP/MTT/TAME khi dataset và learner tương thích; luôn lưu requested/realized và trạng thái tài nguyên.</x:v>
       </x:c>
       <x:c r="E9" s="30" t="s">
+        <x:v>330</x:v>
+      </x:c>
+      <x:c r="F9" s="33" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="G9" s="30" t="s">
         <x:v>332</x:v>
       </x:c>
-      <x:c r="F9" s="33" t="s">
+      <x:c r="H9" s="30" t="s">
         <x:v>333</x:v>
-      </x:c>
-      <x:c r="G9" s="30" t="s">
-        <x:v>334</x:v>
-      </x:c>
-      <x:c r="H9" s="30" t="s">
-        <x:v>335</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="88" customHeight="1">
@@ -6649,25 +6825,25 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B10" s="39" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="C10" s="30" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="D10" s="30" t="s">
         <x:v>336</x:v>
       </x:c>
-      <x:c r="C10" s="30" t="s">
+      <x:c r="E10" s="30" t="s">
         <x:v>337</x:v>
       </x:c>
-      <x:c r="D10" s="30" t="s">
+      <x:c r="F10" s="33" t="s">
         <x:v>338</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="s">
+      <x:c r="G10" s="30" t="s">
         <x:v>339</x:v>
       </x:c>
-      <x:c r="F10" s="33" t="s">
+      <x:c r="H10" s="30" t="s">
         <x:v>340</x:v>
-      </x:c>
-      <x:c r="G10" s="30" t="s">
-        <x:v>341</x:v>
-      </x:c>
-      <x:c r="H10" s="30" t="s">
-        <x:v>342</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="88" customHeight="1">
@@ -6675,25 +6851,25 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B11" s="41" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="C11" s="30" t="s">
+        <x:v>342</x:v>
+      </x:c>
+      <x:c r="D11" s="30" t="s">
         <x:v>343</x:v>
       </x:c>
-      <x:c r="C11" s="30" t="s">
+      <x:c r="E11" s="30" t="s">
         <x:v>344</x:v>
       </x:c>
-      <x:c r="D11" s="30" t="s">
+      <x:c r="F11" s="33" t="s">
         <x:v>345</x:v>
       </x:c>
-      <x:c r="E11" s="30" t="s">
+      <x:c r="G11" s="30" t="s">
         <x:v>346</x:v>
       </x:c>
-      <x:c r="F11" s="33" t="s">
+      <x:c r="H11" s="30" t="s">
         <x:v>347</x:v>
-      </x:c>
-      <x:c r="G11" s="30" t="s">
-        <x:v>348</x:v>
-      </x:c>
-      <x:c r="H11" s="30" t="s">
-        <x:v>349</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="88" customHeight="1">
@@ -6701,25 +6877,25 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B12" s="41" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="C12" s="30" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="D12" s="30" t="s">
         <x:v>350</x:v>
       </x:c>
-      <x:c r="C12" s="30" t="s">
+      <x:c r="E12" s="30" t="s">
         <x:v>351</x:v>
       </x:c>
-      <x:c r="D12" s="30" t="s">
+      <x:c r="F12" s="33" t="s">
         <x:v>352</x:v>
       </x:c>
-      <x:c r="E12" s="30" t="s">
+      <x:c r="G12" s="30" t="s">
         <x:v>353</x:v>
       </x:c>
-      <x:c r="F12" s="33" t="s">
+      <x:c r="H12" s="30" t="s">
         <x:v>354</x:v>
-      </x:c>
-      <x:c r="G12" s="30" t="s">
-        <x:v>355</x:v>
-      </x:c>
-      <x:c r="H12" s="30" t="s">
-        <x:v>356</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="88" customHeight="1">
@@ -6727,25 +6903,25 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B13" s="35" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="C13" s="30" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="D13" s="30" t="s">
         <x:v>357</x:v>
       </x:c>
-      <x:c r="C13" s="30" t="s">
+      <x:c r="E13" s="30" t="s">
         <x:v>358</x:v>
       </x:c>
-      <x:c r="D13" s="30" t="s">
+      <x:c r="F13" s="33" t="s">
         <x:v>359</x:v>
       </x:c>
-      <x:c r="E13" s="30" t="s">
+      <x:c r="G13" s="30" t="s">
         <x:v>360</x:v>
       </x:c>
-      <x:c r="F13" s="33" t="s">
+      <x:c r="H13" s="30" t="s">
         <x:v>361</x:v>
-      </x:c>
-      <x:c r="G13" s="30" t="s">
-        <x:v>362</x:v>
-      </x:c>
-      <x:c r="H13" s="30" t="s">
-        <x:v>363</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="88" customHeight="1">
@@ -6753,25 +6929,25 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B14" s="35" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="C14" s="30" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="D14" s="30" t="s">
         <x:v>364</x:v>
       </x:c>
-      <x:c r="C14" s="30" t="s">
+      <x:c r="E14" s="30" t="s">
         <x:v>365</x:v>
       </x:c>
-      <x:c r="D14" s="30" t="s">
+      <x:c r="F14" s="33" t="s">
         <x:v>366</x:v>
       </x:c>
-      <x:c r="E14" s="30" t="s">
+      <x:c r="G14" s="30" t="s">
         <x:v>367</x:v>
       </x:c>
-      <x:c r="F14" s="33" t="s">
+      <x:c r="H14" s="30" t="s">
         <x:v>368</x:v>
-      </x:c>
-      <x:c r="G14" s="30" t="s">
-        <x:v>369</x:v>
-      </x:c>
-      <x:c r="H14" s="30" t="s">
-        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="88" customHeight="1">
@@ -6782,22 +6958,22 @@
         <x:v>104</x:v>
       </x:c>
       <x:c r="C15" s="30" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="D15" s="30" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="E15" s="30" t="s">
         <x:v>371</x:v>
       </x:c>
-      <x:c r="D15" s="30" t="s">
+      <x:c r="F15" s="33" t="s">
         <x:v>372</x:v>
       </x:c>
-      <x:c r="E15" s="30" t="s">
+      <x:c r="G15" s="30" t="s">
         <x:v>373</x:v>
       </x:c>
-      <x:c r="F15" s="33" t="s">
+      <x:c r="H15" s="30" t="s">
         <x:v>374</x:v>
-      </x:c>
-      <x:c r="G15" s="30" t="s">
-        <x:v>375</x:v>
-      </x:c>
-      <x:c r="H15" s="30" t="s">
-        <x:v>376</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="88" customHeight="1">
@@ -6805,25 +6981,25 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B16" s="32" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="C16" s="30" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="D16" s="30" t="s">
         <x:v>377</x:v>
       </x:c>
-      <x:c r="C16" s="30" t="s">
+      <x:c r="E16" s="30" t="s">
         <x:v>378</x:v>
       </x:c>
-      <x:c r="D16" s="30" t="s">
+      <x:c r="F16" s="33" t="s">
         <x:v>379</x:v>
       </x:c>
-      <x:c r="E16" s="30" t="s">
+      <x:c r="G16" s="30" t="s">
         <x:v>380</x:v>
       </x:c>
-      <x:c r="F16" s="33" t="s">
+      <x:c r="H16" s="30" t="s">
         <x:v>381</x:v>
-      </x:c>
-      <x:c r="G16" s="30" t="s">
-        <x:v>382</x:v>
-      </x:c>
-      <x:c r="H16" s="30" t="s">
-        <x:v>383</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="88" customHeight="1">
@@ -6831,25 +7007,25 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B17" s="32" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="C17" s="30" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="D17" s="30" t="s">
         <x:v>384</x:v>
       </x:c>
-      <x:c r="C17" s="30" t="s">
+      <x:c r="E17" s="30" t="s">
         <x:v>385</x:v>
       </x:c>
-      <x:c r="D17" s="30" t="s">
+      <x:c r="F17" s="33" t="s">
         <x:v>386</x:v>
       </x:c>
-      <x:c r="E17" s="30" t="s">
+      <x:c r="G17" s="30" t="s">
         <x:v>387</x:v>
       </x:c>
-      <x:c r="F17" s="33" t="s">
+      <x:c r="H17" s="30" t="s">
         <x:v>388</x:v>
-      </x:c>
-      <x:c r="G17" s="30" t="s">
-        <x:v>389</x:v>
-      </x:c>
-      <x:c r="H17" s="30" t="s">
-        <x:v>390</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -6864,7 +7040,7 @@
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="64" t="s">
-        <x:v>391</x:v>
+        <x:v>389</x:v>
       </x:c>
       <x:c r="B19" s="65"/>
       <x:c r="C19" s="65"/>
@@ -6876,11 +7052,11 @@
     </x:row>
     <x:row r="20" ht="35" customHeight="1">
       <x:c r="A20" s="67" t="s">
-        <x:v>392</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B20" s="68"/>
       <x:c r="C20" s="59" t="s">
-        <x:v>393</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="D20" s="59"/>
       <x:c r="E20" s="59"/>
@@ -6890,11 +7066,11 @@
     </x:row>
     <x:row r="21" ht="35" customHeight="1">
       <x:c r="A21" s="67" t="s">
-        <x:v>394</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="B21" s="68"/>
       <x:c r="C21" s="59" t="s">
-        <x:v>395</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="D21" s="59"/>
       <x:c r="E21" s="59"/>
@@ -6904,11 +7080,11 @@
     </x:row>
     <x:row r="22" ht="35" customHeight="1">
       <x:c r="A22" s="67" t="s">
-        <x:v>396</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="B22" s="68"/>
       <x:c r="C22" s="59" t="s">
-        <x:v>397</x:v>
+        <x:v>395</x:v>
       </x:c>
       <x:c r="D22" s="59"/>
       <x:c r="E22" s="59"/>
@@ -6918,11 +7094,11 @@
     </x:row>
     <x:row r="23" ht="35" customHeight="1">
       <x:c r="A23" s="67" t="s">
-        <x:v>398</x:v>
+        <x:v>396</x:v>
       </x:c>
       <x:c r="B23" s="68"/>
       <x:c r="C23" s="59" t="s">
-        <x:v>399</x:v>
+        <x:v>397</x:v>
       </x:c>
       <x:c r="D23" s="59"/>
       <x:c r="E23" s="59"/>
@@ -6932,11 +7108,11 @@
     </x:row>
     <x:row r="24" ht="35" customHeight="1">
       <x:c r="A24" s="67" t="s">
-        <x:v>400</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B24" s="68"/>
       <x:c r="C24" s="59" t="s">
-        <x:v>401</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="D24" s="59"/>
       <x:c r="E24" s="59"/>
@@ -6983,7 +7159,7 @@
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="50" t="s">
-        <x:v>402</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="B1" s="50"/>
       <x:c r="C1" s="50"/>
@@ -6997,7 +7173,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="51" t="s">
-        <x:v>403</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="B2" s="51"/>
       <x:c r="C2" s="51"/>
@@ -7011,7 +7187,7 @@
     </x:row>
     <x:row r="3" ht="26" customHeight="1">
       <x:c r="A3" s="63" t="s">
-        <x:v>404</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="B3" s="63"/>
       <x:c r="C3" s="63"/>
@@ -7037,258 +7213,258 @@
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="17" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="B5" s="17" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="C5" s="17" t="s">
         <x:v>405</x:v>
       </x:c>
-      <x:c r="B5" s="17" t="s">
+      <x:c r="D5" s="17" t="s">
         <x:v>406</x:v>
       </x:c>
-      <x:c r="C5" s="17" t="s">
+      <x:c r="E5" s="17" t="s">
         <x:v>407</x:v>
       </x:c>
-      <x:c r="D5" s="17" t="s">
+      <x:c r="F5" s="17" t="s">
         <x:v>408</x:v>
       </x:c>
-      <x:c r="E5" s="17" t="s">
+      <x:c r="G5" s="17" t="s">
         <x:v>409</x:v>
       </x:c>
-      <x:c r="F5" s="17" t="s">
+      <x:c r="H5" s="17" t="s">
         <x:v>410</x:v>
       </x:c>
-      <x:c r="G5" s="17" t="s">
+      <x:c r="I5" s="17" t="s">
         <x:v>411</x:v>
       </x:c>
-      <x:c r="H5" s="17" t="s">
+      <x:c r="J5" s="17" t="s">
         <x:v>412</x:v>
-      </x:c>
-      <x:c r="I5" s="17" t="s">
-        <x:v>413</x:v>
-      </x:c>
-      <x:c r="J5" s="17" t="s">
-        <x:v>414</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="95" customHeight="1">
       <x:c r="A6" s="34" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B6" s="42" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="C6" s="34" t="s">
         <x:v>415</x:v>
-      </x:c>
-      <x:c r="B6" s="42" t="s">
-        <x:v>416</x:v>
-      </x:c>
-      <x:c r="C6" s="34" t="s">
-        <x:v>417</x:v>
       </x:c>
       <x:c r="D6" s="34" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E6" s="30" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="F6" s="30" t="s">
+        <x:v>417</x:v>
+      </x:c>
+      <x:c r="G6" s="30" t="s">
         <x:v>418</x:v>
       </x:c>
-      <x:c r="F6" s="30" t="s">
+      <x:c r="H6" s="30" t="s">
         <x:v>419</x:v>
       </x:c>
-      <x:c r="G6" s="30" t="s">
+      <x:c r="I6" s="30" t="s">
         <x:v>420</x:v>
       </x:c>
-      <x:c r="H6" s="30" t="s">
+      <x:c r="J6" s="30" t="s">
         <x:v>421</x:v>
-      </x:c>
-      <x:c r="I6" s="30" t="s">
-        <x:v>422</x:v>
-      </x:c>
-      <x:c r="J6" s="30" t="s">
-        <x:v>423</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="95" customHeight="1">
       <x:c r="A7" s="34" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="B7" s="42" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="C7" s="34" t="s">
         <x:v>424</x:v>
-      </x:c>
-      <x:c r="B7" s="42" t="s">
-        <x:v>425</x:v>
-      </x:c>
-      <x:c r="C7" s="34" t="s">
-        <x:v>426</x:v>
       </x:c>
       <x:c r="D7" s="34" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E7" s="30" t="s">
+        <x:v>425</x:v>
+      </x:c>
+      <x:c r="F7" s="30" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="G7" s="30" t="s">
         <x:v>427</x:v>
       </x:c>
-      <x:c r="F7" s="30" t="s">
+      <x:c r="H7" s="30" t="s">
         <x:v>428</x:v>
       </x:c>
-      <x:c r="G7" s="30" t="s">
+      <x:c r="I7" s="30" t="s">
         <x:v>429</x:v>
       </x:c>
-      <x:c r="H7" s="30" t="s">
+      <x:c r="J7" s="30" t="s">
         <x:v>430</x:v>
-      </x:c>
-      <x:c r="I7" s="30" t="s">
-        <x:v>431</x:v>
-      </x:c>
-      <x:c r="J7" s="30" t="s">
-        <x:v>432</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="95" customHeight="1">
       <x:c r="A8" s="34" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="B8" s="42" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="C8" s="34" t="s">
         <x:v>433</x:v>
-      </x:c>
-      <x:c r="B8" s="42" t="s">
-        <x:v>434</x:v>
-      </x:c>
-      <x:c r="C8" s="34" t="s">
-        <x:v>435</x:v>
       </x:c>
       <x:c r="D8" s="34" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E8" s="30" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="F8" s="30" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="G8" s="30" t="s">
         <x:v>436</x:v>
       </x:c>
-      <x:c r="F8" s="30" t="s">
+      <x:c r="H8" s="30" t="s">
         <x:v>437</x:v>
       </x:c>
-      <x:c r="G8" s="30" t="s">
+      <x:c r="I8" s="30" t="s">
         <x:v>438</x:v>
       </x:c>
-      <x:c r="H8" s="30" t="s">
+      <x:c r="J8" s="30" t="s">
         <x:v>439</x:v>
-      </x:c>
-      <x:c r="I8" s="30" t="s">
-        <x:v>440</x:v>
-      </x:c>
-      <x:c r="J8" s="30" t="s">
-        <x:v>441</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="95" customHeight="1">
       <x:c r="A9" s="34" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="B9" s="42" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="C9" s="34" t="s">
         <x:v>442</x:v>
-      </x:c>
-      <x:c r="B9" s="42" t="s">
-        <x:v>443</x:v>
-      </x:c>
-      <x:c r="C9" s="34" t="s">
-        <x:v>444</x:v>
       </x:c>
       <x:c r="D9" s="34" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="E9" s="30" t="s">
+        <x:v>443</x:v>
+      </x:c>
+      <x:c r="F9" s="30" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="G9" s="30" t="s">
         <x:v>445</x:v>
       </x:c>
-      <x:c r="F9" s="30" t="s">
+      <x:c r="H9" s="30" t="s">
         <x:v>446</x:v>
       </x:c>
-      <x:c r="G9" s="30" t="s">
+      <x:c r="I9" s="30" t="s">
         <x:v>447</x:v>
       </x:c>
-      <x:c r="H9" s="30" t="s">
+      <x:c r="J9" s="30" t="s">
         <x:v>448</x:v>
-      </x:c>
-      <x:c r="I9" s="30" t="s">
-        <x:v>449</x:v>
-      </x:c>
-      <x:c r="J9" s="30" t="s">
-        <x:v>450</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="95" customHeight="1">
       <x:c r="A10" s="34" t="s">
-        <x:v>451</x:v>
+        <x:v>449</x:v>
       </x:c>
       <x:c r="B10" s="42" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="C10" s="34" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="D10" s="34" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="E10" s="30" t="s">
         <x:v>452</x:v>
       </x:c>
-      <x:c r="D10" s="34" t="s">
+      <x:c r="F10" s="30" t="s">
         <x:v>453</x:v>
       </x:c>
-      <x:c r="E10" s="30" t="s">
+      <x:c r="G10" s="30" t="s">
         <x:v>454</x:v>
       </x:c>
-      <x:c r="F10" s="30" t="s">
+      <x:c r="H10" s="30" t="s">
         <x:v>455</x:v>
       </x:c>
-      <x:c r="G10" s="30" t="s">
+      <x:c r="I10" s="30" t="s">
         <x:v>456</x:v>
       </x:c>
-      <x:c r="H10" s="30" t="s">
+      <x:c r="J10" s="30" t="s">
         <x:v>457</x:v>
-      </x:c>
-      <x:c r="I10" s="30" t="s">
-        <x:v>458</x:v>
-      </x:c>
-      <x:c r="J10" s="30" t="s">
-        <x:v>459</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="95" customHeight="1">
       <x:c r="A11" s="38" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="B11" s="43" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="C11" s="38" t="s">
         <x:v>460</x:v>
       </x:c>
-      <x:c r="B11" s="43" t="s">
+      <x:c r="D11" s="38" t="s">
         <x:v>461</x:v>
       </x:c>
-      <x:c r="C11" s="38" t="s">
+      <x:c r="E11" s="30" t="s">
         <x:v>462</x:v>
       </x:c>
-      <x:c r="D11" s="38" t="s">
+      <x:c r="F11" s="30" t="s">
         <x:v>463</x:v>
       </x:c>
-      <x:c r="E11" s="30" t="s">
+      <x:c r="G11" s="30" t="s">
         <x:v>464</x:v>
       </x:c>
-      <x:c r="F11" s="30" t="s">
+      <x:c r="H11" s="30" t="s">
         <x:v>465</x:v>
       </x:c>
-      <x:c r="G11" s="30" t="s">
+      <x:c r="I11" s="30" t="s">
         <x:v>466</x:v>
       </x:c>
-      <x:c r="H11" s="30" t="s">
+      <x:c r="J11" s="30" t="s">
         <x:v>467</x:v>
-      </x:c>
-      <x:c r="I11" s="30" t="s">
-        <x:v>468</x:v>
-      </x:c>
-      <x:c r="J11" s="30" t="s">
-        <x:v>469</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="95" customHeight="1">
       <x:c r="A12" s="38" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B12" s="43" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="C12" s="38" t="s">
         <x:v>470</x:v>
       </x:c>
-      <x:c r="B12" s="43" t="s">
+      <x:c r="D12" s="38" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="E12" s="30" t="s">
         <x:v>471</x:v>
       </x:c>
-      <x:c r="C12" s="38" t="s">
+      <x:c r="F12" s="30" t="s">
         <x:v>472</x:v>
       </x:c>
-      <x:c r="D12" s="38" t="s">
-        <x:v>463</x:v>
-      </x:c>
-      <x:c r="E12" s="30" t="s">
+      <x:c r="G12" s="30" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="H12" s="30" t="s">
         <x:v>473</x:v>
       </x:c>
-      <x:c r="F12" s="30" t="s">
+      <x:c r="I12" s="30" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="J12" s="30" t="s">
         <x:v>474</x:v>
-      </x:c>
-      <x:c r="G12" s="30" t="s">
-        <x:v>466</x:v>
-      </x:c>
-      <x:c r="H12" s="30" t="s">
-        <x:v>475</x:v>
-      </x:c>
-      <x:c r="I12" s="30" t="s">
-        <x:v>468</x:v>
-      </x:c>
-      <x:c r="J12" s="30" t="s">
-        <x:v>476</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -7305,7 +7481,7 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="64" t="s">
-        <x:v>477</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="B14" s="65"/>
       <x:c r="C14" s="65"/>
@@ -7319,11 +7495,11 @@
     </x:row>
     <x:row r="15" ht="38" customHeight="1">
       <x:c r="A15" s="67" t="s">
-        <x:v>478</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="B15" s="68"/>
       <x:c r="C15" s="59" t="s">
-        <x:v>479</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="D15" s="59"/>
       <x:c r="E15" s="59"/>
@@ -7335,11 +7511,11 @@
     </x:row>
     <x:row r="16" ht="38" customHeight="1">
       <x:c r="A16" s="67" t="s">
-        <x:v>480</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="B16" s="68"/>
       <x:c r="C16" s="59" t="s">
-        <x:v>481</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="D16" s="59"/>
       <x:c r="E16" s="59"/>
@@ -7351,11 +7527,11 @@
     </x:row>
     <x:row r="17" ht="38" customHeight="1">
       <x:c r="A17" s="67" t="s">
-        <x:v>482</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="B17" s="68"/>
       <x:c r="C17" s="59" t="s">
-        <x:v>483</x:v>
+        <x:v>481</x:v>
       </x:c>
       <x:c r="D17" s="59"/>
       <x:c r="E17" s="59"/>
@@ -7367,11 +7543,11 @@
     </x:row>
     <x:row r="18" ht="38" customHeight="1">
       <x:c r="A18" s="67" t="s">
-        <x:v>484</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B18" s="68"/>
       <x:c r="C18" s="59" t="s">
-        <x:v>485</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="D18" s="59"/>
       <x:c r="E18" s="59"/>
@@ -7438,7 +7614,7 @@
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="50" t="s">
-        <x:v>486</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="B1" s="50"/>
       <x:c r="C1" s="50"/>
@@ -7452,7 +7628,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="51" t="s">
-        <x:v>487</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="B2" s="51"/>
       <x:c r="C2" s="51"/>
@@ -7466,7 +7642,7 @@
     </x:row>
     <x:row r="3" ht="29" customHeight="1">
       <x:c r="A3" s="63" t="s">
-        <x:v>488</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="B3" s="63"/>
       <x:c r="C3" s="63"/>
@@ -7492,7 +7668,7 @@
     </x:row>
     <x:row r="5" ht="42" customHeight="1">
       <x:c r="A5" s="17" t="s">
-        <x:v>405</x:v>
+        <x:v>403</x:v>
       </x:c>
       <x:c r="B5" s="17" t="s">
         <x:v>4</x:v>
@@ -7501,25 +7677,25 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="D5" s="17" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="E5" s="17" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="F5" s="17" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="G5" s="17" t="s">
         <x:v>489</x:v>
       </x:c>
-      <x:c r="E5" s="17" t="s">
-        <x:v>484</x:v>
-      </x:c>
-      <x:c r="F5" s="17" t="s">
+      <x:c r="H5" s="17" t="s">
         <x:v>490</x:v>
       </x:c>
-      <x:c r="G5" s="17" t="s">
+      <x:c r="I5" s="17" t="s">
         <x:v>491</x:v>
       </x:c>
-      <x:c r="H5" s="17" t="s">
+      <x:c r="J5" s="17" t="s">
         <x:v>492</x:v>
-      </x:c>
-      <x:c r="I5" s="17" t="s">
-        <x:v>493</x:v>
-      </x:c>
-      <x:c r="J5" s="17" t="s">
-        <x:v>494</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="88" customHeight="1">
@@ -7530,28 +7706,28 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="C6" s="27" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="D6" s="19" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="E6" s="19" t="s">
         <x:v>495</x:v>
       </x:c>
-      <x:c r="D6" s="19" t="s">
+      <x:c r="F6" s="18" t="s">
         <x:v>496</x:v>
       </x:c>
-      <x:c r="E6" s="19" t="s">
+      <x:c r="G6" s="18" t="s">
         <x:v>497</x:v>
       </x:c>
-      <x:c r="F6" s="18" t="s">
+      <x:c r="H6" s="18" t="s">
         <x:v>498</x:v>
       </x:c>
-      <x:c r="G6" s="18" t="s">
+      <x:c r="I6" s="18" t="s">
         <x:v>499</x:v>
       </x:c>
-      <x:c r="H6" s="18" t="s">
+      <x:c r="J6" s="18" t="s">
         <x:v>500</x:v>
-      </x:c>
-      <x:c r="I6" s="18" t="s">
-        <x:v>501</x:v>
-      </x:c>
-      <x:c r="J6" s="18" t="s">
-        <x:v>502</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="88" customHeight="1">
@@ -7594,28 +7770,28 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="C8" s="25" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="E8" s="19" t="s">
         <x:v>503</x:v>
       </x:c>
-      <x:c r="D8" s="19" t="s">
+      <x:c r="F8" s="18" t="s">
         <x:v>504</x:v>
       </x:c>
-      <x:c r="E8" s="19" t="s">
+      <x:c r="G8" s="18" t="s">
         <x:v>505</x:v>
       </x:c>
-      <x:c r="F8" s="18" t="s">
+      <x:c r="H8" s="18" t="s">
         <x:v>506</x:v>
       </x:c>
-      <x:c r="G8" s="18" t="s">
+      <x:c r="I8" s="18" t="s">
         <x:v>507</x:v>
       </x:c>
-      <x:c r="H8" s="18" t="s">
+      <x:c r="J8" s="18" t="s">
         <x:v>508</x:v>
-      </x:c>
-      <x:c r="I8" s="18" t="s">
-        <x:v>509</x:v>
-      </x:c>
-      <x:c r="J8" s="18" t="s">
-        <x:v>510</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="88" customHeight="1">
@@ -7626,28 +7802,28 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C9" s="25" t="s">
-        <x:v>503</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="D9" s="19" t="s">
-        <x:v>504</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="E9" s="19" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="F9" s="18" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="G9" s="18" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="H9" s="18" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="I9" s="18" t="s">
         <x:v>511</x:v>
       </x:c>
-      <x:c r="F9" s="18" t="s">
-        <x:v>512</x:v>
-      </x:c>
-      <x:c r="G9" s="18" t="s">
-        <x:v>507</x:v>
-      </x:c>
-      <x:c r="H9" s="18" t="s">
+      <x:c r="J9" s="18" t="s">
         <x:v>508</x:v>
-      </x:c>
-      <x:c r="I9" s="18" t="s">
-        <x:v>513</x:v>
-      </x:c>
-      <x:c r="J9" s="18" t="s">
-        <x:v>510</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="88" customHeight="1">
@@ -7658,28 +7834,28 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C10" s="25" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="E10" s="19" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="F10" s="18" t="s">
         <x:v>514</x:v>
       </x:c>
-      <x:c r="D10" s="19" t="s">
-        <x:v>504</x:v>
-      </x:c>
-      <x:c r="E10" s="19" t="s">
+      <x:c r="G10" s="18" t="s">
         <x:v>515</x:v>
       </x:c>
-      <x:c r="F10" s="18" t="s">
+      <x:c r="H10" s="18" t="s">
         <x:v>516</x:v>
       </x:c>
-      <x:c r="G10" s="18" t="s">
+      <x:c r="I10" s="18" t="s">
         <x:v>517</x:v>
       </x:c>
-      <x:c r="H10" s="18" t="s">
+      <x:c r="J10" s="18" t="s">
         <x:v>518</x:v>
-      </x:c>
-      <x:c r="I10" s="18" t="s">
-        <x:v>519</x:v>
-      </x:c>
-      <x:c r="J10" s="18" t="s">
-        <x:v>520</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="88" customHeight="1">
@@ -7690,28 +7866,28 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="C11" s="25" t="s">
-        <x:v>514</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="D11" s="19" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="E11" s="19" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="F11" s="18" t="s">
         <x:v>521</x:v>
       </x:c>
-      <x:c r="E11" s="19" t="s">
+      <x:c r="G11" s="18" t="s">
         <x:v>522</x:v>
       </x:c>
-      <x:c r="F11" s="18" t="s">
+      <x:c r="H11" s="18" t="s">
         <x:v>523</x:v>
       </x:c>
-      <x:c r="G11" s="18" t="s">
+      <x:c r="I11" s="18" t="s">
         <x:v>524</x:v>
       </x:c>
-      <x:c r="H11" s="18" t="s">
+      <x:c r="J11" s="18" t="s">
         <x:v>525</x:v>
-      </x:c>
-      <x:c r="I11" s="18" t="s">
-        <x:v>526</x:v>
-      </x:c>
-      <x:c r="J11" s="18" t="s">
-        <x:v>527</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="88" customHeight="1">
@@ -7748,77 +7924,77 @@
     </x:row>
     <x:row r="13" ht="88" customHeight="1">
       <x:c r="A13" s="25" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="B13" s="26" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="C13" s="25" t="s">
         <x:v>528</x:v>
       </x:c>
-      <x:c r="B13" s="26" t="s">
+      <x:c r="D13" s="19" t="s">
         <x:v>529</x:v>
       </x:c>
-      <x:c r="C13" s="25" t="s">
+      <x:c r="E13" s="19" t="s">
         <x:v>530</x:v>
       </x:c>
-      <x:c r="D13" s="19" t="s">
+      <x:c r="F13" s="18" t="s">
         <x:v>531</x:v>
       </x:c>
-      <x:c r="E13" s="19" t="s">
+      <x:c r="G13" s="18" t="s">
         <x:v>532</x:v>
       </x:c>
-      <x:c r="F13" s="18" t="s">
+      <x:c r="H13" s="18" t="s">
         <x:v>533</x:v>
       </x:c>
-      <x:c r="G13" s="18" t="s">
+      <x:c r="I13" s="18" t="s">
         <x:v>534</x:v>
       </x:c>
-      <x:c r="H13" s="18" t="s">
+      <x:c r="J13" s="18" t="s">
         <x:v>535</x:v>
-      </x:c>
-      <x:c r="I13" s="18" t="s">
-        <x:v>536</x:v>
-      </x:c>
-      <x:c r="J13" s="18" t="s">
-        <x:v>537</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="88" customHeight="1">
       <x:c r="A14" s="25" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="B14" s="26" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="C14" s="25" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="D14" s="19" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="E14" s="19" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="F14" s="18" t="s">
         <x:v>538</x:v>
       </x:c>
-      <x:c r="B14" s="26" t="s">
+      <x:c r="G14" s="18" t="s">
         <x:v>539</x:v>
       </x:c>
-      <x:c r="C14" s="25" t="s">
-        <x:v>530</x:v>
-      </x:c>
-      <x:c r="D14" s="19" t="s">
-        <x:v>531</x:v>
-      </x:c>
-      <x:c r="E14" s="19" t="s">
-        <x:v>532</x:v>
-      </x:c>
-      <x:c r="F14" s="18" t="s">
+      <x:c r="H14" s="18" t="s">
         <x:v>540</x:v>
       </x:c>
-      <x:c r="G14" s="18" t="s">
+      <x:c r="I14" s="18" t="s">
         <x:v>541</x:v>
       </x:c>
-      <x:c r="H14" s="18" t="s">
-        <x:v>542</x:v>
-      </x:c>
-      <x:c r="I14" s="18" t="s">
-        <x:v>543</x:v>
-      </x:c>
       <x:c r="J14" s="18" t="s">
-        <x:v>537</x:v>
+        <x:v>535</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="88" customHeight="1">
       <x:c r="A15" s="20" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="B15" s="21" t="s">
+        <x:v>543</x:v>
+      </x:c>
+      <x:c r="C15" s="20" t="s">
         <x:v>544</x:v>
-      </x:c>
-      <x:c r="B15" s="21" t="s">
-        <x:v>545</x:v>
-      </x:c>
-      <x:c r="C15" s="20" t="s">
-        <x:v>546</x:v>
       </x:c>
       <x:c r="D15" s="19" t="str">
         <x:v>requested 5%; realized source-feasible</x:v>
@@ -7839,18 +8015,18 @@
         <x:v>Không còn trần 500. Adult: requested 1.384, realized 1.332; OOM/timeout phải ghi đúng trạng thái và ngưỡng.</x:v>
       </x:c>
       <x:c r="J15" s="18" t="s">
-        <x:v>547</x:v>
+        <x:v>545</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="88" customHeight="1">
       <x:c r="A16" s="20" t="s">
-        <x:v>548</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="B16" s="21" t="s">
-        <x:v>549</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="C16" s="20" t="s">
-        <x:v>546</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="D16" s="19" t="str">
         <x:v>requested 5%; realized theo contract</x:v>
@@ -7876,115 +8052,115 @@
     </x:row>
     <x:row r="17" ht="88" customHeight="1">
       <x:c r="A17" s="44" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="B17" s="45" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="C17" s="44" t="s">
         <x:v>550</x:v>
       </x:c>
-      <x:c r="B17" s="45" t="s">
+      <x:c r="D17" s="19" t="s">
         <x:v>551</x:v>
       </x:c>
-      <x:c r="C17" s="44" t="s">
+      <x:c r="E17" s="19" t="s">
         <x:v>552</x:v>
       </x:c>
-      <x:c r="D17" s="19" t="s">
+      <x:c r="F17" s="18" t="s">
         <x:v>553</x:v>
       </x:c>
-      <x:c r="E17" s="19" t="s">
+      <x:c r="G17" s="18" t="s">
         <x:v>554</x:v>
       </x:c>
-      <x:c r="F17" s="18" t="s">
+      <x:c r="H17" s="18" t="s">
         <x:v>555</x:v>
       </x:c>
-      <x:c r="G17" s="18" t="s">
+      <x:c r="I17" s="18" t="s">
         <x:v>556</x:v>
       </x:c>
-      <x:c r="H17" s="18" t="s">
+      <x:c r="J17" s="18" t="s">
         <x:v>557</x:v>
-      </x:c>
-      <x:c r="I17" s="18" t="s">
-        <x:v>558</x:v>
-      </x:c>
-      <x:c r="J17" s="18" t="s">
-        <x:v>559</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="88" customHeight="1">
       <x:c r="A18" s="44" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="B18" s="45" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="C18" s="44" t="s">
         <x:v>560</x:v>
       </x:c>
-      <x:c r="B18" s="45" t="s">
+      <x:c r="D18" s="19" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="E18" s="19" t="s">
         <x:v>561</x:v>
       </x:c>
-      <x:c r="C18" s="44" t="s">
+      <x:c r="F18" s="18" t="s">
         <x:v>562</x:v>
       </x:c>
-      <x:c r="D18" s="19" t="s">
-        <x:v>553</x:v>
-      </x:c>
-      <x:c r="E18" s="19" t="s">
+      <x:c r="G18" s="18" t="s">
         <x:v>563</x:v>
       </x:c>
-      <x:c r="F18" s="18" t="s">
+      <x:c r="H18" s="18" t="s">
         <x:v>564</x:v>
       </x:c>
-      <x:c r="G18" s="18" t="s">
+      <x:c r="I18" s="18" t="s">
         <x:v>565</x:v>
       </x:c>
-      <x:c r="H18" s="18" t="s">
+      <x:c r="J18" s="18" t="s">
         <x:v>566</x:v>
-      </x:c>
-      <x:c r="I18" s="18" t="s">
-        <x:v>567</x:v>
-      </x:c>
-      <x:c r="J18" s="18" t="s">
-        <x:v>568</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="88" customHeight="1">
       <x:c r="A19" s="44" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="B19" s="45" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="C19" s="44" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="D19" s="19" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="E19" s="19" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="F19" s="18" t="s">
         <x:v>569</x:v>
       </x:c>
-      <x:c r="B19" s="45" t="s">
+      <x:c r="G19" s="18" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="H19" s="18" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="I19" s="18" t="s">
         <x:v>570</x:v>
       </x:c>
-      <x:c r="C19" s="44" t="s">
-        <x:v>562</x:v>
-      </x:c>
-      <x:c r="D19" s="19" t="s">
-        <x:v>553</x:v>
-      </x:c>
-      <x:c r="E19" s="19" t="s">
-        <x:v>563</x:v>
-      </x:c>
-      <x:c r="F19" s="18" t="s">
+      <x:c r="J19" s="18" t="s">
         <x:v>571</x:v>
-      </x:c>
-      <x:c r="G19" s="18" t="s">
-        <x:v>565</x:v>
-      </x:c>
-      <x:c r="H19" s="18" t="s">
-        <x:v>566</x:v>
-      </x:c>
-      <x:c r="I19" s="18" t="s">
-        <x:v>572</x:v>
-      </x:c>
-      <x:c r="J19" s="18" t="s">
-        <x:v>573</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="88" customHeight="1">
       <x:c r="A20" s="44" t="s">
-        <x:v>574</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="B20" s="45" t="s">
-        <x:v>575</x:v>
+        <x:v>573</x:v>
       </x:c>
       <x:c r="C20" s="44" t="s">
-        <x:v>562</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="D20" s="19" t="str">
         <x:v>cap_at_candidate_pool</x:v>
       </x:c>
       <x:c r="E20" s="19" t="s">
-        <x:v>576</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="F20" s="18" t="str">
         <x:v>Mục tiêu 5% do protocol thực nghiệm đặt ra, không phải giới hạn của repo BDIS. P03 dùng realized=min(requested 5%, số dòng BDIS pool), sau đó vẫn chạy phân bổ structure×class, RFF herding và simplex-QP. Không pad, không lặp dòng.</x:v>
@@ -7993,7 +8169,7 @@
         <x:v>Weighted real rows từ BDIS candidate pool; bắt buộc lưu requested_rows, realized_rows và realized_ratio.</x:v>
       </x:c>
       <x:c r="H20" s="18" t="s">
-        <x:v>566</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="I20" s="18" t="str">
         <x:v>Chỉ chạy khi BDIS native SUCCESS. Pool nhỏ hơn 5% không phải OOM hay budget failure; dùng toàn pool và đánh giá utility kèm size thực. Adult: requested=1.384, BDIS/realized=1.083 (3,913%).</x:v>
@@ -8010,10 +8186,10 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="C21" s="44" t="s">
-        <x:v>577</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D21" s="19" t="s">
-        <x:v>553</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="E21" s="19" t="str">
         <x:v>s1 dev trước freeze; s2 confirm sau freeze</x:v>
@@ -8022,16 +8198,16 @@
         <x:v>Một OOF query loss chỉ từ train; s1 dùng parent N02 khai báo trước; h=[√α·a, √(1−α)·l]; α∈{0.25,0.50,0.75}, default 0.50.</x:v>
       </x:c>
       <x:c r="G21" s="18" t="s">
-        <x:v>578</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="H21" s="18" t="s">
-        <x:v>579</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="I21" s="18" t="str">
         <x:v>s1: pre_freeze_dev_screen, confirmatory_eligible=false. s2/test cần freeze manifest và parent khớp winner.</x:v>
       </x:c>
       <x:c r="J21" s="18" t="s">
-        <x:v>580</x:v>
+        <x:v>578</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="88" customHeight="1">
@@ -8042,10 +8218,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="C22" s="44" t="s">
-        <x:v>577</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="D22" s="19" t="s">
-        <x:v>553</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="E22" s="19" t="str">
         <x:v>s1 dev trước freeze; s2 confirm sau freeze</x:v>
@@ -8054,16 +8230,16 @@
         <x:v>Portfolio OOF query learners đăng ký trước, chỉ dùng train; s1 dùng parent N02; cùng α grid và normalization như P04.</x:v>
       </x:c>
       <x:c r="G22" s="18" t="s">
-        <x:v>581</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="H22" s="18" t="s">
-        <x:v>579</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="I22" s="18" t="str">
         <x:v>s1: pre_freeze_dev_screen, confirmatory_eligible=false. s2/test cần freeze manifest; không đổi portfolio sau test.</x:v>
       </x:c>
       <x:c r="J22" s="18" t="s">
-        <x:v>580</x:v>
+        <x:v>578</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="88" customHeight="1">
@@ -8074,28 +8250,28 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="C23" s="24" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="D23" s="19" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="E23" s="19" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="F23" s="18" t="s">
         <x:v>582</x:v>
       </x:c>
-      <x:c r="D23" s="19" t="s">
-        <x:v>553</x:v>
-      </x:c>
-      <x:c r="E23" s="19" t="s">
+      <x:c r="G23" s="18" t="s">
         <x:v>583</x:v>
       </x:c>
-      <x:c r="F23" s="18" t="s">
+      <x:c r="H23" s="18" t="s">
         <x:v>584</x:v>
       </x:c>
-      <x:c r="G23" s="18" t="s">
+      <x:c r="I23" s="18" t="s">
         <x:v>585</x:v>
       </x:c>
-      <x:c r="H23" s="18" t="s">
+      <x:c r="J23" s="18" t="s">
         <x:v>586</x:v>
-      </x:c>
-      <x:c r="I23" s="18" t="s">
-        <x:v>587</x:v>
-      </x:c>
-      <x:c r="J23" s="18" t="s">
-        <x:v>588</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="88" customHeight="1">
@@ -8106,28 +8282,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="C24" s="24" t="s">
-        <x:v>582</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="D24" s="19" t="s">
-        <x:v>553</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="E24" s="19" t="s">
-        <x:v>583</x:v>
+        <x:v>581</x:v>
       </x:c>
       <x:c r="F24" s="18" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="G24" s="18" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="H24" s="18" t="s">
         <x:v>589</x:v>
       </x:c>
-      <x:c r="G24" s="18" t="s">
+      <x:c r="I24" s="18" t="s">
         <x:v>590</x:v>
       </x:c>
-      <x:c r="H24" s="18" t="s">
-        <x:v>591</x:v>
-      </x:c>
-      <x:c r="I24" s="18" t="s">
-        <x:v>592</x:v>
-      </x:c>
       <x:c r="J24" s="18" t="s">
-        <x:v>588</x:v>
+        <x:v>586</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="88" customHeight="1">
@@ -8138,28 +8314,28 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="C25" s="24" t="s">
-        <x:v>582</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="D25" s="19" t="s">
-        <x:v>553</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="E25" s="19" t="str">
         <x:v>Dùng P05 cùng run ở s1; dùng @proposed_winner sau freeze ở s2</x:v>
       </x:c>
       <x:c r="F25" s="18" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="G25" s="18" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="H25" s="18" t="s">
         <x:v>593</x:v>
       </x:c>
-      <x:c r="G25" s="18" t="s">
+      <x:c r="I25" s="18" t="s">
         <x:v>594</x:v>
       </x:c>
-      <x:c r="H25" s="18" t="s">
-        <x:v>595</x:v>
-      </x:c>
-      <x:c r="I25" s="18" t="s">
-        <x:v>596</x:v>
-      </x:c>
       <x:c r="J25" s="18" t="s">
-        <x:v>588</x:v>
+        <x:v>586</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -8384,6 +8560,70 @@
       </x:c>
       <x:c r="J32" s="76" t="str">
         <x:v>inwonakng/tdbench@0b3ee8…357; adapter khai báo patch</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="28.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A33" s="73" t="str">
+        <x:v>P10</x:v>
+      </x:c>
+      <x:c r="B33" s="74" t="str">
+        <x:v>SKQ-MR-CoreTab-XGB</x:v>
+      </x:c>
+      <x:c r="C33" s="73" t="str">
+        <x:v>Proposed scale-out</x:v>
+      </x:c>
+      <x:c r="D33" s="75" t="str">
+        <x:v>exact_total</x:v>
+      </x:c>
+      <x:c r="E33" s="75" t="str">
+        <x:v>Screen [11,29,47]</x:v>
+      </x:c>
+      <x:c r="F33" s="76" t="str">
+        <x:v>Chia train thành shard cân bằng tối đa 10.000 dòng; chạy CoreTab-XGB official-source trong từng shard; gộp leaf nhỏ còn tối đa 64 parent/shard; SKQ RFF streaming + herding + simplex-QP cấp exact budget toàn cục.</x:v>
+      </x:c>
+      <x:c r="G33" s="76" t="str">
+        <x:v>Weighted real rows; diagnostics shard/parent/RFF; toàn bộ index thuộc train gốc.</x:v>
+      </x:c>
+      <x:c r="H33" s="76" t="str">
+        <x:v>Mass-preserving simplex-QP.</x:v>
+      </x:c>
+      <x:c r="I33" s="76" t="str">
+        <x:v>Declared adapter/proposed, không claim CoreTab native equivalence. Mọi train row được dùng; không proxy. Mục tiêu giảm peak RAM và số dòng trong mỗi phép biến đổi/QP.</x:v>
+      </x:c>
+      <x:c r="J33" s="76" t="str">
+        <x:v>Project method + CoreTab locked source; config full-v4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="28.799999237060547" hidden="0" customHeight="1">
+      <x:c r="A34" s="73" t="str">
+        <x:v>P11</x:v>
+      </x:c>
+      <x:c r="B34" s="74" t="str">
+        <x:v>SKQ-MR-BDIS</x:v>
+      </x:c>
+      <x:c r="C34" s="73" t="str">
+        <x:v>Proposed scale-out</x:v>
+      </x:c>
+      <x:c r="D34" s="75" t="str">
+        <x:v>cap_at_candidate_pool</x:v>
+      </x:c>
+      <x:c r="E34" s="75" t="str">
+        <x:v>Screen [11,29,47]</x:v>
+      </x:c>
+      <x:c r="F34" s="76" t="str">
+        <x:v>Chia train thành shard cân bằng tối đa 10.000 dòng; chạy BDIS official-source trong từng shard; hợp candidate; SKQ RFF streaming + herding + simplex-QP reduce toàn cục.</x:v>
+      </x:c>
+      <x:c r="G34" s="76" t="str">
+        <x:v>Weighted real rows từ union BDIS candidates; requested/realized + shard diagnostics.</x:v>
+      </x:c>
+      <x:c r="H34" s="76" t="str">
+        <x:v>Mass-preserving simplex-QP.</x:v>
+      </x:c>
+      <x:c r="I34" s="76" t="str">
+        <x:v>Declared adapter/proposed, không claim BDIS native equivalence. realized=min(5%, union candidate); không pad/trùng; mọi train row tham gia parent structure.</x:v>
+      </x:c>
+      <x:c r="J34" s="76" t="str">
+        <x:v>Project method + BDIS locked source; config full-v4</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -8416,7 +8656,7 @@
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
       <x:c r="A1" s="50" t="s">
-        <x:v>597</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="B1" s="50"/>
       <x:c r="C1" s="50"/>
@@ -8430,7 +8670,7 @@
     </x:row>
     <x:row r="2" ht="29" customHeight="1">
       <x:c r="A2" s="51" t="s">
-        <x:v>598</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="B2" s="51"/>
       <x:c r="C2" s="51"/>
@@ -8444,7 +8684,7 @@
     </x:row>
     <x:row r="3" ht="27" customHeight="1">
       <x:c r="A3" s="63" t="s">
-        <x:v>599</x:v>
+        <x:v>597</x:v>
       </x:c>
       <x:c r="B3" s="63"/>
       <x:c r="C3" s="63"/>
@@ -8476,28 +8716,28 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="17" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="D5" s="17" t="s">
+        <x:v>599</x:v>
+      </x:c>
+      <x:c r="E5" s="17" t="s">
         <x:v>600</x:v>
       </x:c>
-      <x:c r="D5" s="17" t="s">
+      <x:c r="F5" s="17" t="s">
         <x:v>601</x:v>
       </x:c>
-      <x:c r="E5" s="17" t="s">
+      <x:c r="G5" s="17" t="s">
         <x:v>602</x:v>
       </x:c>
-      <x:c r="F5" s="17" t="s">
+      <x:c r="H5" s="17" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="I5" s="17" t="s">
         <x:v>603</x:v>
       </x:c>
-      <x:c r="G5" s="17" t="s">
+      <x:c r="J5" s="17" t="s">
         <x:v>604</x:v>
-      </x:c>
-      <x:c r="H5" s="17" t="s">
-        <x:v>407</x:v>
-      </x:c>
-      <x:c r="I5" s="17" t="s">
-        <x:v>605</x:v>
-      </x:c>
-      <x:c r="J5" s="17" t="s">
-        <x:v>606</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="55" customHeight="1">
@@ -8505,31 +8745,31 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B6" s="27" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="C6" s="46" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="D6" s="19" t="s">
         <x:v>607</x:v>
       </x:c>
-      <x:c r="C6" s="46" t="s">
+      <x:c r="E6" s="18" t="s">
         <x:v>608</x:v>
       </x:c>
-      <x:c r="D6" s="19" t="s">
+      <x:c r="F6" s="18" t="s">
         <x:v>609</x:v>
       </x:c>
-      <x:c r="E6" s="18" t="s">
+      <x:c r="G6" s="18" t="s">
         <x:v>610</x:v>
-      </x:c>
-      <x:c r="F6" s="18" t="s">
-        <x:v>611</x:v>
-      </x:c>
-      <x:c r="G6" s="18" t="s">
-        <x:v>612</x:v>
       </x:c>
       <x:c r="H6" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I6" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J6" s="18" t="s">
-        <x:v>614</x:v>
+        <x:v>612</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="55" customHeight="1">
@@ -8537,31 +8777,31 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C7" s="46" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="D7" s="19" t="s">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="E7" s="18" t="s">
         <x:v>615</x:v>
       </x:c>
-      <x:c r="D7" s="19" t="s">
+      <x:c r="F7" s="18" t="s">
         <x:v>616</x:v>
       </x:c>
-      <x:c r="E7" s="18" t="s">
+      <x:c r="G7" s="18" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="H7" s="19" t="s">
         <x:v>617</x:v>
       </x:c>
-      <x:c r="F7" s="18" t="s">
+      <x:c r="I7" s="19" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="J7" s="18" t="s">
         <x:v>618</x:v>
-      </x:c>
-      <x:c r="G7" s="18" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="H7" s="19" t="s">
-        <x:v>619</x:v>
-      </x:c>
-      <x:c r="I7" s="19" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="J7" s="18" t="s">
-        <x:v>620</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="55" customHeight="1">
@@ -8569,31 +8809,31 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B8" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C8" s="46" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="D8" s="19" t="s">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="E8" s="18" t="s">
         <x:v>621</x:v>
       </x:c>
-      <x:c r="D8" s="19" t="s">
-        <x:v>622</x:v>
-      </x:c>
-      <x:c r="E8" s="18" t="s">
-        <x:v>623</x:v>
-      </x:c>
       <x:c r="F8" s="18" t="s">
-        <x:v>618</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="G8" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H8" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I8" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J8" s="18" t="s">
-        <x:v>624</x:v>
+        <x:v>622</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="55" customHeight="1">
@@ -8601,31 +8841,31 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C9" s="46" t="s">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="D9" s="19" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="E9" s="18" t="s">
         <x:v>625</x:v>
       </x:c>
-      <x:c r="D9" s="19" t="s">
+      <x:c r="F9" s="18" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="G9" s="18" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="H9" s="19" t="s">
         <x:v>626</x:v>
       </x:c>
-      <x:c r="E9" s="18" t="s">
+      <x:c r="I9" s="19" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="J9" s="18" t="s">
         <x:v>627</x:v>
-      </x:c>
-      <x:c r="F9" s="18" t="s">
-        <x:v>618</x:v>
-      </x:c>
-      <x:c r="G9" s="18" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="H9" s="19" t="s">
-        <x:v>628</x:v>
-      </x:c>
-      <x:c r="I9" s="19" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="J9" s="18" t="s">
-        <x:v>629</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="55" customHeight="1">
@@ -8633,31 +8873,31 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C10" s="46" t="s">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="D10" s="19" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="E10" s="18" t="s">
         <x:v>630</x:v>
       </x:c>
-      <x:c r="D10" s="19" t="s">
-        <x:v>631</x:v>
-      </x:c>
-      <x:c r="E10" s="18" t="s">
-        <x:v>632</x:v>
-      </x:c>
       <x:c r="F10" s="18" t="s">
-        <x:v>618</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="G10" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H10" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I10" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J10" s="18" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="55" customHeight="1">
@@ -8665,31 +8905,31 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B11" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C11" s="46" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="D11" s="19" t="s">
+        <x:v>633</x:v>
+      </x:c>
+      <x:c r="E11" s="18" t="s">
         <x:v>634</x:v>
       </x:c>
-      <x:c r="D11" s="19" t="s">
-        <x:v>635</x:v>
-      </x:c>
-      <x:c r="E11" s="18" t="s">
-        <x:v>636</x:v>
-      </x:c>
       <x:c r="F11" s="18" t="s">
-        <x:v>618</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="G11" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H11" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I11" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J11" s="18" t="s">
-        <x:v>637</x:v>
+        <x:v>635</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="55" customHeight="1">
@@ -8697,31 +8937,31 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C12" s="46" t="s">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="D12" s="19" t="s">
+        <x:v>637</x:v>
+      </x:c>
+      <x:c r="E12" s="18" t="s">
         <x:v>638</x:v>
       </x:c>
-      <x:c r="D12" s="19" t="s">
-        <x:v>639</x:v>
-      </x:c>
-      <x:c r="E12" s="18" t="s">
-        <x:v>640</x:v>
-      </x:c>
       <x:c r="F12" s="18" t="s">
-        <x:v>618</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="G12" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H12" s="19" t="s">
-        <x:v>628</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="I12" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J12" s="18" t="s">
-        <x:v>629</x:v>
+        <x:v>627</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="55" customHeight="1">
@@ -8729,31 +8969,31 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B13" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C13" s="46" t="s">
+        <x:v>639</x:v>
+      </x:c>
+      <x:c r="D13" s="19" t="s">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="E13" s="18" t="s">
         <x:v>641</x:v>
       </x:c>
-      <x:c r="D13" s="19" t="s">
-        <x:v>642</x:v>
-      </x:c>
-      <x:c r="E13" s="18" t="s">
-        <x:v>643</x:v>
-      </x:c>
       <x:c r="F13" s="18" t="s">
-        <x:v>618</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="G13" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H13" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I13" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J13" s="18" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="55" customHeight="1">
@@ -8761,31 +9001,31 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B14" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C14" s="46" t="s">
+        <x:v>642</x:v>
+      </x:c>
+      <x:c r="D14" s="19" t="s">
+        <x:v>643</x:v>
+      </x:c>
+      <x:c r="E14" s="18" t="s">
         <x:v>644</x:v>
       </x:c>
-      <x:c r="D14" s="19" t="s">
+      <x:c r="F14" s="18" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="G14" s="18" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="H14" s="47" t="s">
         <x:v>645</x:v>
       </x:c>
-      <x:c r="E14" s="18" t="s">
+      <x:c r="I14" s="19" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="J14" s="18" t="s">
         <x:v>646</x:v>
-      </x:c>
-      <x:c r="F14" s="18" t="s">
-        <x:v>618</x:v>
-      </x:c>
-      <x:c r="G14" s="18" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="H14" s="47" t="s">
-        <x:v>647</x:v>
-      </x:c>
-      <x:c r="I14" s="19" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="J14" s="18" t="s">
-        <x:v>648</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="55" customHeight="1">
@@ -8793,31 +9033,31 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B15" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C15" s="46" t="s">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="D15" s="19" t="s">
+        <x:v>648</x:v>
+      </x:c>
+      <x:c r="E15" s="18" t="s">
         <x:v>649</x:v>
       </x:c>
-      <x:c r="D15" s="19" t="s">
-        <x:v>650</x:v>
-      </x:c>
-      <x:c r="E15" s="18" t="s">
-        <x:v>651</x:v>
-      </x:c>
       <x:c r="F15" s="18" t="s">
-        <x:v>618</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="G15" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H15" s="19" t="s">
-        <x:v>628</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="I15" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J15" s="18" t="s">
-        <x:v>629</x:v>
+        <x:v>627</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="55" customHeight="1">
@@ -8825,31 +9065,31 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B16" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C16" s="46" t="s">
+        <x:v>650</x:v>
+      </x:c>
+      <x:c r="D16" s="19" t="s">
+        <x:v>651</x:v>
+      </x:c>
+      <x:c r="E16" s="18" t="s">
         <x:v>652</x:v>
       </x:c>
-      <x:c r="D16" s="19" t="s">
-        <x:v>653</x:v>
-      </x:c>
-      <x:c r="E16" s="18" t="s">
-        <x:v>654</x:v>
-      </x:c>
       <x:c r="F16" s="18" t="s">
-        <x:v>618</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="G16" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H16" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I16" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J16" s="18" t="s">
-        <x:v>655</x:v>
+        <x:v>653</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="55" customHeight="1">
@@ -8857,31 +9097,31 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B17" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C17" s="46" t="s">
+        <x:v>654</x:v>
+      </x:c>
+      <x:c r="D17" s="19" t="s">
+        <x:v>655</x:v>
+      </x:c>
+      <x:c r="E17" s="18" t="s">
         <x:v>656</x:v>
       </x:c>
-      <x:c r="D17" s="19" t="s">
-        <x:v>657</x:v>
-      </x:c>
-      <x:c r="E17" s="18" t="s">
-        <x:v>658</x:v>
-      </x:c>
       <x:c r="F17" s="18" t="s">
-        <x:v>618</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="G17" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H17" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I17" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J17" s="18" t="s">
-        <x:v>659</x:v>
+        <x:v>657</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="55" customHeight="1">
@@ -8889,31 +9129,31 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B18" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C18" s="46" t="s">
+        <x:v>658</x:v>
+      </x:c>
+      <x:c r="D18" s="19" t="s">
+        <x:v>659</x:v>
+      </x:c>
+      <x:c r="E18" s="18" t="s">
         <x:v>660</x:v>
       </x:c>
-      <x:c r="D18" s="19" t="s">
+      <x:c r="F18" s="18" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="G18" s="18" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="H18" s="19" t="s">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="I18" s="19" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="J18" s="18" t="s">
         <x:v>661</x:v>
-      </x:c>
-      <x:c r="E18" s="18" t="s">
-        <x:v>662</x:v>
-      </x:c>
-      <x:c r="F18" s="18" t="s">
-        <x:v>618</x:v>
-      </x:c>
-      <x:c r="G18" s="18" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="H18" s="19" t="s">
-        <x:v>628</x:v>
-      </x:c>
-      <x:c r="I18" s="19" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="J18" s="18" t="s">
-        <x:v>663</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="55" customHeight="1">
@@ -8921,31 +9161,31 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B19" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C19" s="46" t="s">
+        <x:v>662</x:v>
+      </x:c>
+      <x:c r="D19" s="19" t="s">
+        <x:v>663</x:v>
+      </x:c>
+      <x:c r="E19" s="18" t="s">
         <x:v>664</x:v>
       </x:c>
-      <x:c r="D19" s="19" t="s">
-        <x:v>665</x:v>
-      </x:c>
-      <x:c r="E19" s="18" t="s">
-        <x:v>666</x:v>
-      </x:c>
       <x:c r="F19" s="18" t="s">
-        <x:v>618</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="G19" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H19" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I19" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J19" s="18" t="s">
-        <x:v>633</x:v>
+        <x:v>631</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="55" customHeight="1">
@@ -8953,31 +9193,31 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B20" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C20" s="46" t="s">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="D20" s="19" t="s">
+        <x:v>666</x:v>
+      </x:c>
+      <x:c r="E20" s="18" t="s">
         <x:v>667</x:v>
       </x:c>
-      <x:c r="D20" s="19" t="s">
+      <x:c r="F20" s="18" t="s">
         <x:v>668</x:v>
       </x:c>
-      <x:c r="E20" s="18" t="s">
+      <x:c r="G20" s="18" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="H20" s="19" t="s">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="I20" s="19" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="J20" s="18" t="s">
         <x:v>669</x:v>
-      </x:c>
-      <x:c r="F20" s="18" t="s">
-        <x:v>670</x:v>
-      </x:c>
-      <x:c r="G20" s="18" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="H20" s="19" t="s">
-        <x:v>619</x:v>
-      </x:c>
-      <x:c r="I20" s="19" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="J20" s="18" t="s">
-        <x:v>671</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="55" customHeight="1">
@@ -8985,31 +9225,31 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B21" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C21" s="46" t="s">
+        <x:v>670</x:v>
+      </x:c>
+      <x:c r="D21" s="19" t="s">
+        <x:v>671</x:v>
+      </x:c>
+      <x:c r="E21" s="18" t="s">
         <x:v>672</x:v>
       </x:c>
-      <x:c r="D21" s="19" t="s">
-        <x:v>673</x:v>
-      </x:c>
-      <x:c r="E21" s="18" t="s">
-        <x:v>674</x:v>
-      </x:c>
       <x:c r="F21" s="18" t="s">
-        <x:v>618</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="G21" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H21" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I21" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J21" s="18" t="s">
-        <x:v>675</x:v>
+        <x:v>673</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="55" customHeight="1">
@@ -9017,31 +9257,31 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B22" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C22" s="46" t="s">
+        <x:v>674</x:v>
+      </x:c>
+      <x:c r="D22" s="19" t="s">
+        <x:v>675</x:v>
+      </x:c>
+      <x:c r="E22" s="18" t="s">
         <x:v>676</x:v>
       </x:c>
-      <x:c r="D22" s="19" t="s">
+      <x:c r="F22" s="18" t="s">
         <x:v>677</x:v>
       </x:c>
-      <x:c r="E22" s="18" t="s">
+      <x:c r="G22" s="18" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="H22" s="19" t="s">
         <x:v>678</x:v>
       </x:c>
-      <x:c r="F22" s="18" t="s">
+      <x:c r="I22" s="19" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="J22" s="18" t="s">
         <x:v>679</x:v>
-      </x:c>
-      <x:c r="G22" s="18" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="H22" s="19" t="s">
-        <x:v>680</x:v>
-      </x:c>
-      <x:c r="I22" s="19" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="J22" s="18" t="s">
-        <x:v>681</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="55" customHeight="1">
@@ -9049,31 +9289,31 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B23" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C23" s="46" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="D23" s="19" t="s">
+        <x:v>681</x:v>
+      </x:c>
+      <x:c r="E23" s="18" t="s">
         <x:v>682</x:v>
       </x:c>
-      <x:c r="D23" s="19" t="s">
+      <x:c r="F23" s="18" t="s">
         <x:v>683</x:v>
       </x:c>
-      <x:c r="E23" s="18" t="s">
-        <x:v>684</x:v>
-      </x:c>
-      <x:c r="F23" s="18" t="s">
-        <x:v>685</x:v>
-      </x:c>
       <x:c r="G23" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H23" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I23" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J23" s="18" t="s">
-        <x:v>686</x:v>
+        <x:v>684</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="55" customHeight="1">
@@ -9081,31 +9321,31 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B24" s="27" t="s">
-        <x:v>607</x:v>
+        <x:v>605</x:v>
       </x:c>
       <x:c r="C24" s="46" t="s">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="D24" s="19" t="s">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="E24" s="18" t="s">
         <x:v>687</x:v>
       </x:c>
-      <x:c r="D24" s="19" t="s">
+      <x:c r="F24" s="18" t="s">
         <x:v>688</x:v>
       </x:c>
-      <x:c r="E24" s="18" t="s">
-        <x:v>689</x:v>
-      </x:c>
-      <x:c r="F24" s="18" t="s">
-        <x:v>690</x:v>
-      </x:c>
       <x:c r="G24" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H24" s="19" t="s">
-        <x:v>619</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="I24" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J24" s="18" t="s">
-        <x:v>686</x:v>
+        <x:v>684</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="55" customHeight="1">
@@ -9113,31 +9353,31 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B25" s="48" t="s">
+        <x:v>689</x:v>
+      </x:c>
+      <x:c r="C25" s="46" t="s">
+        <x:v>690</x:v>
+      </x:c>
+      <x:c r="D25" s="19" t="s">
         <x:v>691</x:v>
       </x:c>
-      <x:c r="C25" s="46" t="s">
+      <x:c r="E25" s="18" t="s">
         <x:v>692</x:v>
       </x:c>
-      <x:c r="D25" s="19" t="s">
+      <x:c r="F25" s="18" t="s">
         <x:v>693</x:v>
       </x:c>
-      <x:c r="E25" s="18" t="s">
+      <x:c r="G25" s="18" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="H25" s="19" t="s">
         <x:v>694</x:v>
       </x:c>
-      <x:c r="F25" s="18" t="s">
+      <x:c r="I25" s="19" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="J25" s="18" t="s">
         <x:v>695</x:v>
-      </x:c>
-      <x:c r="G25" s="18" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="H25" s="19" t="s">
-        <x:v>696</x:v>
-      </x:c>
-      <x:c r="I25" s="19" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="J25" s="18" t="s">
-        <x:v>697</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="55" customHeight="1">
@@ -9145,31 +9385,31 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B26" s="48" t="s">
-        <x:v>691</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="C26" s="46" t="s">
+        <x:v>696</x:v>
+      </x:c>
+      <x:c r="D26" s="19" t="s">
+        <x:v>697</x:v>
+      </x:c>
+      <x:c r="E26" s="18" t="s">
         <x:v>698</x:v>
       </x:c>
-      <x:c r="D26" s="19" t="s">
+      <x:c r="F26" s="18" t="s">
         <x:v>699</x:v>
       </x:c>
-      <x:c r="E26" s="18" t="s">
+      <x:c r="G26" s="18" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="H26" s="19" t="s">
+        <x:v>694</x:v>
+      </x:c>
+      <x:c r="I26" s="19" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="J26" s="18" t="s">
         <x:v>700</x:v>
-      </x:c>
-      <x:c r="F26" s="18" t="s">
-        <x:v>701</x:v>
-      </x:c>
-      <x:c r="G26" s="18" t="s">
-        <x:v>612</x:v>
-      </x:c>
-      <x:c r="H26" s="19" t="s">
-        <x:v>696</x:v>
-      </x:c>
-      <x:c r="I26" s="19" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="J26" s="18" t="s">
-        <x:v>702</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="55" customHeight="1">
@@ -9177,31 +9417,31 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B27" s="48" t="s">
-        <x:v>691</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="C27" s="46" t="s">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c r="D27" s="19" t="s">
+        <x:v>702</x:v>
+      </x:c>
+      <x:c r="E27" s="18" t="s">
         <x:v>703</x:v>
       </x:c>
-      <x:c r="D27" s="19" t="s">
-        <x:v>704</x:v>
-      </x:c>
-      <x:c r="E27" s="18" t="s">
-        <x:v>705</x:v>
-      </x:c>
       <x:c r="F27" s="18" t="s">
-        <x:v>701</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="G27" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H27" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I27" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J27" s="18" t="s">
-        <x:v>706</x:v>
+        <x:v>704</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="55" customHeight="1">
@@ -9209,31 +9449,31 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B28" s="48" t="s">
-        <x:v>691</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="C28" s="46" t="s">
+        <x:v>705</x:v>
+      </x:c>
+      <x:c r="D28" s="19" t="s">
+        <x:v>706</x:v>
+      </x:c>
+      <x:c r="E28" s="18" t="s">
         <x:v>707</x:v>
       </x:c>
-      <x:c r="D28" s="19" t="s">
-        <x:v>708</x:v>
-      </x:c>
-      <x:c r="E28" s="18" t="s">
-        <x:v>709</x:v>
-      </x:c>
       <x:c r="F28" s="18" t="s">
-        <x:v>701</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="G28" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H28" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I28" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J28" s="18" t="s">
-        <x:v>710</x:v>
+        <x:v>708</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="55" customHeight="1">
@@ -9241,31 +9481,31 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B29" s="48" t="s">
-        <x:v>691</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="C29" s="46" t="s">
+        <x:v>709</x:v>
+      </x:c>
+      <x:c r="D29" s="19" t="s">
+        <x:v>710</x:v>
+      </x:c>
+      <x:c r="E29" s="18" t="s">
         <x:v>711</x:v>
       </x:c>
-      <x:c r="D29" s="19" t="s">
+      <x:c r="F29" s="18" t="s">
         <x:v>712</x:v>
       </x:c>
-      <x:c r="E29" s="18" t="s">
-        <x:v>713</x:v>
-      </x:c>
-      <x:c r="F29" s="18" t="s">
-        <x:v>714</x:v>
-      </x:c>
       <x:c r="G29" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H29" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I29" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J29" s="18" t="s">
-        <x:v>716</x:v>
+        <x:v>714</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="55" customHeight="1">
@@ -9273,31 +9513,31 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B30" s="48" t="s">
-        <x:v>691</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="C30" s="46" t="s">
+        <x:v>715</x:v>
+      </x:c>
+      <x:c r="D30" s="19" t="s">
+        <x:v>716</x:v>
+      </x:c>
+      <x:c r="E30" s="18" t="s">
         <x:v>717</x:v>
       </x:c>
-      <x:c r="D30" s="19" t="s">
+      <x:c r="F30" s="18" t="s">
         <x:v>718</x:v>
       </x:c>
-      <x:c r="E30" s="18" t="s">
-        <x:v>719</x:v>
-      </x:c>
-      <x:c r="F30" s="18" t="s">
-        <x:v>720</x:v>
-      </x:c>
       <x:c r="G30" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H30" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I30" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J30" s="18" t="s">
-        <x:v>721</x:v>
+        <x:v>719</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="55" customHeight="1">
@@ -9305,31 +9545,31 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B31" s="48" t="s">
-        <x:v>691</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="C31" s="46" t="s">
+        <x:v>720</x:v>
+      </x:c>
+      <x:c r="D31" s="19" t="s">
+        <x:v>721</x:v>
+      </x:c>
+      <x:c r="E31" s="18" t="s">
         <x:v>722</x:v>
       </x:c>
-      <x:c r="D31" s="19" t="s">
+      <x:c r="F31" s="18" t="s">
         <x:v>723</x:v>
       </x:c>
-      <x:c r="E31" s="18" t="s">
-        <x:v>724</x:v>
-      </x:c>
-      <x:c r="F31" s="18" t="s">
-        <x:v>725</x:v>
-      </x:c>
       <x:c r="G31" s="18" t="s">
-        <x:v>612</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="H31" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I31" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J31" s="18" t="s">
-        <x:v>726</x:v>
+        <x:v>724</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="55" customHeight="1">
@@ -9337,31 +9577,31 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B32" s="25" t="s">
+        <x:v>725</x:v>
+      </x:c>
+      <x:c r="C32" s="46" t="s">
+        <x:v>726</x:v>
+      </x:c>
+      <x:c r="D32" s="19" t="s">
         <x:v>727</x:v>
       </x:c>
-      <x:c r="C32" s="46" t="s">
+      <x:c r="E32" s="18" t="s">
         <x:v>728</x:v>
       </x:c>
-      <x:c r="D32" s="19" t="s">
+      <x:c r="F32" s="18" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="G32" s="18" t="s">
         <x:v>729</x:v>
-      </x:c>
-      <x:c r="E32" s="18" t="s">
-        <x:v>730</x:v>
-      </x:c>
-      <x:c r="F32" s="18" t="s">
-        <x:v>618</x:v>
-      </x:c>
-      <x:c r="G32" s="18" t="s">
-        <x:v>731</x:v>
       </x:c>
       <x:c r="H32" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I32" s="19" t="s">
-        <x:v>732</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="J32" s="18" t="s">
-        <x:v>733</x:v>
+        <x:v>731</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="55" customHeight="1">
@@ -9369,31 +9609,31 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B33" s="25" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="C33" s="46" t="s">
+        <x:v>732</x:v>
+      </x:c>
+      <x:c r="D33" s="19" t="s">
+        <x:v>733</x:v>
+      </x:c>
+      <x:c r="E33" s="18" t="s">
         <x:v>734</x:v>
       </x:c>
-      <x:c r="D33" s="19" t="s">
-        <x:v>735</x:v>
-      </x:c>
-      <x:c r="E33" s="18" t="s">
-        <x:v>736</x:v>
-      </x:c>
       <x:c r="F33" s="18" t="s">
-        <x:v>728</x:v>
+        <x:v>726</x:v>
       </x:c>
       <x:c r="G33" s="18" t="s">
-        <x:v>731</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H33" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I33" s="19" t="s">
-        <x:v>732</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="J33" s="18" t="s">
-        <x:v>737</x:v>
+        <x:v>735</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="55" customHeight="1">
@@ -9401,31 +9641,31 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B34" s="25" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="C34" s="46" t="s">
+        <x:v>736</x:v>
+      </x:c>
+      <x:c r="D34" s="19" t="s">
+        <x:v>737</x:v>
+      </x:c>
+      <x:c r="E34" s="18" t="s">
         <x:v>738</x:v>
       </x:c>
-      <x:c r="D34" s="19" t="s">
-        <x:v>739</x:v>
-      </x:c>
-      <x:c r="E34" s="18" t="s">
-        <x:v>740</x:v>
-      </x:c>
       <x:c r="F34" s="18" t="s">
-        <x:v>611</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="G34" s="18" t="s">
-        <x:v>731</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H34" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I34" s="19" t="s">
-        <x:v>732</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="J34" s="18" t="s">
-        <x:v>741</x:v>
+        <x:v>739</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="55" customHeight="1">
@@ -9433,31 +9673,31 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B35" s="25" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="C35" s="46" t="s">
+        <x:v>740</x:v>
+      </x:c>
+      <x:c r="D35" s="19" t="s">
+        <x:v>741</x:v>
+      </x:c>
+      <x:c r="E35" s="18" t="s">
         <x:v>742</x:v>
       </x:c>
-      <x:c r="D35" s="19" t="s">
+      <x:c r="F35" s="18" t="s">
         <x:v>743</x:v>
       </x:c>
-      <x:c r="E35" s="18" t="s">
-        <x:v>744</x:v>
-      </x:c>
-      <x:c r="F35" s="18" t="s">
-        <x:v>745</x:v>
-      </x:c>
       <x:c r="G35" s="18" t="s">
-        <x:v>731</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H35" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I35" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J35" s="18" t="s">
-        <x:v>671</x:v>
+        <x:v>669</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="55" customHeight="1">
@@ -9465,31 +9705,31 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B36" s="25" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="C36" s="46" t="s">
+        <x:v>744</x:v>
+      </x:c>
+      <x:c r="D36" s="19" t="s">
+        <x:v>745</x:v>
+      </x:c>
+      <x:c r="E36" s="18" t="s">
         <x:v>746</x:v>
       </x:c>
-      <x:c r="D36" s="19" t="s">
-        <x:v>747</x:v>
-      </x:c>
-      <x:c r="E36" s="18" t="s">
-        <x:v>748</x:v>
-      </x:c>
       <x:c r="F36" s="18" t="s">
-        <x:v>745</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="G36" s="18" t="s">
-        <x:v>731</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H36" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I36" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J36" s="18" t="s">
-        <x:v>749</x:v>
+        <x:v>747</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="55" customHeight="1">
@@ -9497,31 +9737,31 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B37" s="25" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="C37" s="46" t="s">
+        <x:v>748</x:v>
+      </x:c>
+      <x:c r="D37" s="19" t="s">
+        <x:v>749</x:v>
+      </x:c>
+      <x:c r="E37" s="18" t="s">
         <x:v>750</x:v>
       </x:c>
-      <x:c r="D37" s="19" t="s">
-        <x:v>751</x:v>
-      </x:c>
-      <x:c r="E37" s="18" t="s">
-        <x:v>752</x:v>
-      </x:c>
       <x:c r="F37" s="18" t="s">
-        <x:v>745</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="G37" s="18" t="s">
-        <x:v>731</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H37" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I37" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J37" s="18" t="s">
-        <x:v>753</x:v>
+        <x:v>751</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="55" customHeight="1">
@@ -9529,31 +9769,31 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B38" s="25" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="C38" s="46" t="s">
+        <x:v>752</x:v>
+      </x:c>
+      <x:c r="D38" s="19" t="s">
+        <x:v>753</x:v>
+      </x:c>
+      <x:c r="E38" s="18" t="s">
         <x:v>754</x:v>
       </x:c>
-      <x:c r="D38" s="19" t="s">
-        <x:v>755</x:v>
-      </x:c>
-      <x:c r="E38" s="18" t="s">
-        <x:v>756</x:v>
-      </x:c>
       <x:c r="F38" s="18" t="s">
-        <x:v>745</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="G38" s="18" t="s">
-        <x:v>731</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H38" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I38" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J38" s="18" t="s">
-        <x:v>671</x:v>
+        <x:v>669</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="55" customHeight="1">
@@ -9561,31 +9801,31 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B39" s="25" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="C39" s="46" t="s">
+        <x:v>755</x:v>
+      </x:c>
+      <x:c r="D39" s="19" t="s">
+        <x:v>756</x:v>
+      </x:c>
+      <x:c r="E39" s="18" t="s">
         <x:v>757</x:v>
       </x:c>
-      <x:c r="D39" s="19" t="s">
+      <x:c r="F39" s="18" t="s">
         <x:v>758</x:v>
       </x:c>
-      <x:c r="E39" s="18" t="s">
-        <x:v>759</x:v>
-      </x:c>
-      <x:c r="F39" s="18" t="s">
-        <x:v>760</x:v>
-      </x:c>
       <x:c r="G39" s="18" t="s">
-        <x:v>731</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H39" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I39" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J39" s="18" t="s">
-        <x:v>761</x:v>
+        <x:v>759</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="55" customHeight="1">
@@ -9593,31 +9833,31 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B40" s="25" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="C40" s="46" t="s">
+        <x:v>760</x:v>
+      </x:c>
+      <x:c r="D40" s="19" t="s">
+        <x:v>761</x:v>
+      </x:c>
+      <x:c r="E40" s="18" t="s">
         <x:v>762</x:v>
       </x:c>
-      <x:c r="D40" s="19" t="s">
+      <x:c r="F40" s="18" t="s">
+        <x:v>758</x:v>
+      </x:c>
+      <x:c r="G40" s="18" t="s">
+        <x:v>729</x:v>
+      </x:c>
+      <x:c r="H40" s="19" t="s">
         <x:v>763</x:v>
       </x:c>
-      <x:c r="E40" s="18" t="s">
+      <x:c r="I40" s="19" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="J40" s="18" t="s">
         <x:v>764</x:v>
-      </x:c>
-      <x:c r="F40" s="18" t="s">
-        <x:v>760</x:v>
-      </x:c>
-      <x:c r="G40" s="18" t="s">
-        <x:v>731</x:v>
-      </x:c>
-      <x:c r="H40" s="19" t="s">
-        <x:v>765</x:v>
-      </x:c>
-      <x:c r="I40" s="19" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="J40" s="18" t="s">
-        <x:v>766</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="55" customHeight="1">
@@ -9625,31 +9865,31 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="B41" s="25" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="C41" s="46" t="s">
+        <x:v>765</x:v>
+      </x:c>
+      <x:c r="D41" s="19" t="s">
+        <x:v>766</x:v>
+      </x:c>
+      <x:c r="E41" s="18" t="s">
         <x:v>767</x:v>
       </x:c>
-      <x:c r="D41" s="19" t="s">
-        <x:v>768</x:v>
-      </x:c>
-      <x:c r="E41" s="18" t="s">
-        <x:v>769</x:v>
-      </x:c>
       <x:c r="F41" s="18" t="s">
-        <x:v>745</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="G41" s="18" t="s">
-        <x:v>731</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H41" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I41" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J41" s="18" t="s">
-        <x:v>753</x:v>
+        <x:v>751</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="55" customHeight="1">
@@ -9657,31 +9897,31 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="B42" s="25" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="C42" s="46" t="s">
+        <x:v>768</x:v>
+      </x:c>
+      <x:c r="D42" s="19" t="s">
+        <x:v>769</x:v>
+      </x:c>
+      <x:c r="E42" s="18" t="s">
         <x:v>770</x:v>
       </x:c>
-      <x:c r="D42" s="19" t="s">
-        <x:v>771</x:v>
-      </x:c>
-      <x:c r="E42" s="18" t="s">
-        <x:v>772</x:v>
-      </x:c>
       <x:c r="F42" s="18" t="s">
-        <x:v>745</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="G42" s="18" t="s">
-        <x:v>731</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H42" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I42" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J42" s="18" t="s">
-        <x:v>749</x:v>
+        <x:v>747</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="55" customHeight="1">
@@ -9689,31 +9929,31 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="B43" s="25" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="C43" s="46" t="s">
+        <x:v>771</x:v>
+      </x:c>
+      <x:c r="D43" s="19" t="s">
+        <x:v>772</x:v>
+      </x:c>
+      <x:c r="E43" s="18" t="s">
         <x:v>773</x:v>
       </x:c>
-      <x:c r="D43" s="19" t="s">
-        <x:v>774</x:v>
-      </x:c>
-      <x:c r="E43" s="18" t="s">
-        <x:v>775</x:v>
-      </x:c>
       <x:c r="F43" s="18" t="s">
-        <x:v>745</x:v>
+        <x:v>743</x:v>
       </x:c>
       <x:c r="G43" s="18" t="s">
-        <x:v>731</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H43" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I43" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J43" s="18" t="s">
-        <x:v>671</x:v>
+        <x:v>669</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="55" customHeight="1">
@@ -9721,31 +9961,31 @@
         <x:v>39</x:v>
       </x:c>
       <x:c r="B44" s="25" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="C44" s="46" t="s">
+        <x:v>774</x:v>
+      </x:c>
+      <x:c r="D44" s="19" t="s">
+        <x:v>775</x:v>
+      </x:c>
+      <x:c r="E44" s="18" t="s">
         <x:v>776</x:v>
       </x:c>
-      <x:c r="D44" s="19" t="s">
+      <x:c r="F44" s="18" t="s">
         <x:v>777</x:v>
       </x:c>
-      <x:c r="E44" s="18" t="s">
-        <x:v>778</x:v>
-      </x:c>
-      <x:c r="F44" s="18" t="s">
-        <x:v>779</x:v>
-      </x:c>
       <x:c r="G44" s="18" t="s">
-        <x:v>731</x:v>
+        <x:v>729</x:v>
       </x:c>
       <x:c r="H44" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I44" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J44" s="18" t="s">
-        <x:v>780</x:v>
+        <x:v>778</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="55" customHeight="1">
@@ -9753,31 +9993,31 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="B45" s="25" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="C45" s="46" t="s">
+        <x:v>779</x:v>
+      </x:c>
+      <x:c r="D45" s="19" t="s">
+        <x:v>780</x:v>
+      </x:c>
+      <x:c r="E45" s="18" t="s">
         <x:v>781</x:v>
       </x:c>
-      <x:c r="D45" s="19" t="s">
+      <x:c r="F45" s="18" t="s">
         <x:v>782</x:v>
       </x:c>
-      <x:c r="E45" s="18" t="s">
+      <x:c r="G45" s="18" t="s">
+        <x:v>729</x:v>
+      </x:c>
+      <x:c r="H45" s="19" t="s">
         <x:v>783</x:v>
       </x:c>
-      <x:c r="F45" s="18" t="s">
+      <x:c r="I45" s="19" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="J45" s="18" t="s">
         <x:v>784</x:v>
-      </x:c>
-      <x:c r="G45" s="18" t="s">
-        <x:v>731</x:v>
-      </x:c>
-      <x:c r="H45" s="19" t="s">
-        <x:v>785</x:v>
-      </x:c>
-      <x:c r="I45" s="19" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="J45" s="18" t="s">
-        <x:v>786</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="55" customHeight="1">
@@ -9785,31 +10025,31 @@
         <x:v>41</x:v>
       </x:c>
       <x:c r="B46" s="25" t="s">
-        <x:v>727</x:v>
+        <x:v>725</x:v>
       </x:c>
       <x:c r="C46" s="46" t="s">
+        <x:v>785</x:v>
+      </x:c>
+      <x:c r="D46" s="19" t="s">
+        <x:v>786</x:v>
+      </x:c>
+      <x:c r="E46" s="18" t="s">
         <x:v>787</x:v>
       </x:c>
-      <x:c r="D46" s="19" t="s">
+      <x:c r="F46" s="18" t="s">
+        <x:v>782</x:v>
+      </x:c>
+      <x:c r="G46" s="18" t="s">
+        <x:v>729</x:v>
+      </x:c>
+      <x:c r="H46" s="19" t="s">
+        <x:v>783</x:v>
+      </x:c>
+      <x:c r="I46" s="19" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="J46" s="18" t="s">
         <x:v>788</x:v>
-      </x:c>
-      <x:c r="E46" s="18" t="s">
-        <x:v>789</x:v>
-      </x:c>
-      <x:c r="F46" s="18" t="s">
-        <x:v>784</x:v>
-      </x:c>
-      <x:c r="G46" s="18" t="s">
-        <x:v>731</x:v>
-      </x:c>
-      <x:c r="H46" s="19" t="s">
-        <x:v>785</x:v>
-      </x:c>
-      <x:c r="I46" s="19" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="J46" s="18" t="s">
-        <x:v>790</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="55" customHeight="1">
@@ -9817,31 +10057,31 @@
         <x:v>42</x:v>
       </x:c>
       <x:c r="B47" s="20" t="s">
+        <x:v>789</x:v>
+      </x:c>
+      <x:c r="C47" s="46" t="s">
+        <x:v>790</x:v>
+      </x:c>
+      <x:c r="D47" s="19" t="s">
         <x:v>791</x:v>
       </x:c>
-      <x:c r="C47" s="46" t="s">
+      <x:c r="E47" s="18" t="s">
         <x:v>792</x:v>
       </x:c>
-      <x:c r="D47" s="19" t="s">
+      <x:c r="F47" s="18" t="s">
         <x:v>793</x:v>
       </x:c>
-      <x:c r="E47" s="18" t="s">
+      <x:c r="G47" s="18" t="s">
         <x:v>794</x:v>
       </x:c>
-      <x:c r="F47" s="18" t="s">
+      <x:c r="H47" s="19" t="s">
         <x:v>795</x:v>
       </x:c>
-      <x:c r="G47" s="18" t="s">
+      <x:c r="I47" s="19" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="J47" s="18" t="s">
         <x:v>796</x:v>
-      </x:c>
-      <x:c r="H47" s="19" t="s">
-        <x:v>797</x:v>
-      </x:c>
-      <x:c r="I47" s="19" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="J47" s="18" t="s">
-        <x:v>798</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="55" customHeight="1">
@@ -9849,31 +10089,31 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="B48" s="20" t="s">
-        <x:v>791</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="C48" s="46" t="s">
+        <x:v>797</x:v>
+      </x:c>
+      <x:c r="D48" s="19" t="s">
+        <x:v>798</x:v>
+      </x:c>
+      <x:c r="E48" s="18" t="s">
         <x:v>799</x:v>
       </x:c>
-      <x:c r="D48" s="19" t="s">
+      <x:c r="F48" s="18" t="s">
         <x:v>800</x:v>
       </x:c>
-      <x:c r="E48" s="18" t="s">
+      <x:c r="G48" s="18" t="s">
         <x:v>801</x:v>
-      </x:c>
-      <x:c r="F48" s="18" t="s">
-        <x:v>802</x:v>
-      </x:c>
-      <x:c r="G48" s="18" t="s">
-        <x:v>803</x:v>
       </x:c>
       <x:c r="H48" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I48" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J48" s="18" t="s">
-        <x:v>804</x:v>
+        <x:v>802</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="55" customHeight="1">
@@ -9881,31 +10121,31 @@
         <x:v>44</x:v>
       </x:c>
       <x:c r="B49" s="20" t="s">
-        <x:v>791</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="C49" s="46" t="s">
+        <x:v>803</x:v>
+      </x:c>
+      <x:c r="D49" s="19" t="s">
+        <x:v>804</x:v>
+      </x:c>
+      <x:c r="E49" s="18" t="s">
         <x:v>805</x:v>
       </x:c>
-      <x:c r="D49" s="19" t="s">
-        <x:v>806</x:v>
-      </x:c>
-      <x:c r="E49" s="18" t="s">
-        <x:v>807</x:v>
-      </x:c>
       <x:c r="F49" s="18" t="s">
-        <x:v>802</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="G49" s="18" t="s">
-        <x:v>803</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="H49" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I49" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J49" s="18" t="s">
-        <x:v>808</x:v>
+        <x:v>806</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="55" customHeight="1">
@@ -9913,31 +10153,31 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="B50" s="20" t="s">
-        <x:v>791</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="C50" s="46" t="s">
+        <x:v>807</x:v>
+      </x:c>
+      <x:c r="D50" s="19" t="s">
+        <x:v>808</x:v>
+      </x:c>
+      <x:c r="E50" s="18" t="s">
         <x:v>809</x:v>
       </x:c>
-      <x:c r="D50" s="19" t="s">
+      <x:c r="F50" s="18" t="s">
         <x:v>810</x:v>
       </x:c>
-      <x:c r="E50" s="18" t="s">
-        <x:v>811</x:v>
-      </x:c>
-      <x:c r="F50" s="18" t="s">
-        <x:v>812</x:v>
-      </x:c>
       <x:c r="G50" s="18" t="s">
-        <x:v>803</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="H50" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I50" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J50" s="18" t="s">
-        <x:v>813</x:v>
+        <x:v>811</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="55" customHeight="1">
@@ -9945,31 +10185,31 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="B51" s="20" t="s">
-        <x:v>791</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="C51" s="46" t="s">
+        <x:v>812</x:v>
+      </x:c>
+      <x:c r="D51" s="19" t="s">
+        <x:v>813</x:v>
+      </x:c>
+      <x:c r="E51" s="18" t="s">
         <x:v>814</x:v>
       </x:c>
-      <x:c r="D51" s="19" t="s">
+      <x:c r="F51" s="18" t="s">
         <x:v>815</x:v>
       </x:c>
-      <x:c r="E51" s="18" t="s">
-        <x:v>816</x:v>
-      </x:c>
-      <x:c r="F51" s="18" t="s">
-        <x:v>817</x:v>
-      </x:c>
       <x:c r="G51" s="18" t="s">
-        <x:v>803</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="H51" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I51" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J51" s="18" t="s">
-        <x:v>818</x:v>
+        <x:v>816</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="55" customHeight="1">
@@ -9977,31 +10217,31 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="B52" s="20" t="s">
-        <x:v>791</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="C52" s="46" t="s">
+        <x:v>817</x:v>
+      </x:c>
+      <x:c r="D52" s="19" t="s">
+        <x:v>818</x:v>
+      </x:c>
+      <x:c r="E52" s="18" t="s">
         <x:v>819</x:v>
       </x:c>
-      <x:c r="D52" s="19" t="s">
-        <x:v>820</x:v>
-      </x:c>
-      <x:c r="E52" s="18" t="s">
-        <x:v>821</x:v>
-      </x:c>
       <x:c r="F52" s="18" t="s">
-        <x:v>817</x:v>
+        <x:v>815</x:v>
       </x:c>
       <x:c r="G52" s="18" t="s">
-        <x:v>803</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="H52" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I52" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J52" s="18" t="s">
-        <x:v>822</x:v>
+        <x:v>820</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="55" customHeight="1">
@@ -10009,31 +10249,31 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="B53" s="20" t="s">
-        <x:v>791</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="C53" s="46" t="s">
+        <x:v>821</x:v>
+      </x:c>
+      <x:c r="D53" s="19" t="s">
+        <x:v>822</x:v>
+      </x:c>
+      <x:c r="E53" s="18" t="s">
         <x:v>823</x:v>
       </x:c>
-      <x:c r="D53" s="19" t="s">
+      <x:c r="F53" s="18" t="s">
         <x:v>824</x:v>
       </x:c>
-      <x:c r="E53" s="18" t="s">
+      <x:c r="G53" s="18" t="s">
         <x:v>825</x:v>
-      </x:c>
-      <x:c r="F53" s="18" t="s">
-        <x:v>826</x:v>
-      </x:c>
-      <x:c r="G53" s="18" t="s">
-        <x:v>827</x:v>
       </x:c>
       <x:c r="H53" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I53" s="19" t="s">
-        <x:v>828</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="J53" s="18" t="s">
-        <x:v>829</x:v>
+        <x:v>827</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="55" customHeight="1">
@@ -10041,31 +10281,31 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="B54" s="20" t="s">
-        <x:v>791</x:v>
+        <x:v>789</x:v>
       </x:c>
       <x:c r="C54" s="46" t="s">
+        <x:v>828</x:v>
+      </x:c>
+      <x:c r="D54" s="19" t="s">
+        <x:v>829</x:v>
+      </x:c>
+      <x:c r="E54" s="18" t="s">
         <x:v>830</x:v>
       </x:c>
-      <x:c r="D54" s="19" t="s">
+      <x:c r="F54" s="18" t="s">
         <x:v>831</x:v>
       </x:c>
-      <x:c r="E54" s="18" t="s">
+      <x:c r="G54" s="18" t="s">
         <x:v>832</x:v>
       </x:c>
-      <x:c r="F54" s="18" t="s">
+      <x:c r="H54" s="19" t="s">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="I54" s="19" t="s">
         <x:v>833</x:v>
       </x:c>
-      <x:c r="G54" s="18" t="s">
+      <x:c r="J54" s="18" t="s">
         <x:v>834</x:v>
-      </x:c>
-      <x:c r="H54" s="19" t="s">
-        <x:v>628</x:v>
-      </x:c>
-      <x:c r="I54" s="19" t="s">
-        <x:v>835</x:v>
-      </x:c>
-      <x:c r="J54" s="18" t="s">
-        <x:v>836</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="55" customHeight="1">
@@ -10073,31 +10313,31 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="B55" s="24" t="s">
+        <x:v>835</x:v>
+      </x:c>
+      <x:c r="C55" s="46" t="s">
+        <x:v>836</x:v>
+      </x:c>
+      <x:c r="D55" s="19" t="s">
         <x:v>837</x:v>
       </x:c>
-      <x:c r="C55" s="46" t="s">
+      <x:c r="E55" s="18" t="s">
         <x:v>838</x:v>
       </x:c>
-      <x:c r="D55" s="19" t="s">
+      <x:c r="F55" s="18" t="s">
         <x:v>839</x:v>
       </x:c>
-      <x:c r="E55" s="18" t="s">
+      <x:c r="G55" s="18" t="s">
         <x:v>840</x:v>
-      </x:c>
-      <x:c r="F55" s="18" t="s">
-        <x:v>841</x:v>
-      </x:c>
-      <x:c r="G55" s="18" t="s">
-        <x:v>842</x:v>
       </x:c>
       <x:c r="H55" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I55" s="19" t="s">
-        <x:v>732</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="J55" s="18" t="s">
-        <x:v>843</x:v>
+        <x:v>841</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="55" customHeight="1">
@@ -10105,31 +10345,31 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="B56" s="24" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C56" s="46" t="s">
+        <x:v>842</x:v>
+      </x:c>
+      <x:c r="D56" s="19" t="s">
+        <x:v>843</x:v>
+      </x:c>
+      <x:c r="E56" s="18" t="s">
         <x:v>844</x:v>
       </x:c>
-      <x:c r="D56" s="19" t="s">
+      <x:c r="F56" s="18" t="s">
         <x:v>845</x:v>
       </x:c>
-      <x:c r="E56" s="18" t="s">
-        <x:v>846</x:v>
-      </x:c>
-      <x:c r="F56" s="18" t="s">
-        <x:v>847</x:v>
-      </x:c>
       <x:c r="G56" s="18" t="s">
-        <x:v>842</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="H56" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I56" s="19" t="s">
-        <x:v>732</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="J56" s="18" t="s">
-        <x:v>848</x:v>
+        <x:v>846</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="55" customHeight="1">
@@ -10137,31 +10377,31 @@
         <x:v>52</x:v>
       </x:c>
       <x:c r="B57" s="24" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C57" s="46" t="s">
+        <x:v>847</x:v>
+      </x:c>
+      <x:c r="D57" s="19" t="s">
+        <x:v>848</x:v>
+      </x:c>
+      <x:c r="E57" s="18" t="s">
         <x:v>849</x:v>
       </x:c>
-      <x:c r="D57" s="19" t="s">
+      <x:c r="F57" s="18" t="s">
         <x:v>850</x:v>
       </x:c>
-      <x:c r="E57" s="18" t="s">
-        <x:v>851</x:v>
-      </x:c>
-      <x:c r="F57" s="18" t="s">
-        <x:v>852</x:v>
-      </x:c>
       <x:c r="G57" s="18" t="s">
-        <x:v>842</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="H57" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I57" s="19" t="s">
-        <x:v>853</x:v>
+        <x:v>851</x:v>
       </x:c>
       <x:c r="J57" s="18" t="s">
-        <x:v>854</x:v>
+        <x:v>852</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="55" customHeight="1">
@@ -10169,22 +10409,22 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="B58" s="24" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C58" s="46" t="s">
+        <x:v>853</x:v>
+      </x:c>
+      <x:c r="D58" s="19" t="s">
+        <x:v>854</x:v>
+      </x:c>
+      <x:c r="E58" s="18" t="s">
         <x:v>855</x:v>
       </x:c>
-      <x:c r="D58" s="19" t="s">
+      <x:c r="F58" s="18" t="s">
         <x:v>856</x:v>
       </x:c>
-      <x:c r="E58" s="18" t="s">
+      <x:c r="G58" s="18" t="s">
         <x:v>857</x:v>
-      </x:c>
-      <x:c r="F58" s="18" t="s">
-        <x:v>858</x:v>
-      </x:c>
-      <x:c r="G58" s="18" t="s">
-        <x:v>859</x:v>
       </x:c>
       <x:c r="H58" s="19" t="s">
         <x:v>19</x:v>
@@ -10194,7 +10434,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J58" s="18" t="s">
-        <x:v>860</x:v>
+        <x:v>858</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="55" customHeight="1">
@@ -10202,22 +10442,22 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="B59" s="24" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C59" s="46" t="s">
+        <x:v>859</x:v>
+      </x:c>
+      <x:c r="D59" s="19" t="s">
+        <x:v>860</x:v>
+      </x:c>
+      <x:c r="E59" s="18" t="s">
         <x:v>861</x:v>
       </x:c>
-      <x:c r="D59" s="19" t="s">
+      <x:c r="F59" s="18" t="s">
         <x:v>862</x:v>
       </x:c>
-      <x:c r="E59" s="18" t="s">
-        <x:v>863</x:v>
-      </x:c>
-      <x:c r="F59" s="18" t="s">
-        <x:v>864</x:v>
-      </x:c>
       <x:c r="G59" s="18" t="s">
-        <x:v>842</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="H59" s="19" t="s">
         <x:v>19</x:v>
@@ -10227,7 +10467,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J59" s="18" t="s">
-        <x:v>865</x:v>
+        <x:v>863</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="55" customHeight="1">
@@ -10235,31 +10475,31 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="B60" s="24" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C60" s="46" t="s">
+        <x:v>864</x:v>
+      </x:c>
+      <x:c r="D60" s="19" t="s">
+        <x:v>865</x:v>
+      </x:c>
+      <x:c r="E60" s="18" t="s">
         <x:v>866</x:v>
       </x:c>
-      <x:c r="D60" s="19" t="s">
+      <x:c r="F60" s="18" t="s">
         <x:v>867</x:v>
       </x:c>
-      <x:c r="E60" s="18" t="s">
+      <x:c r="G60" s="18" t="s">
         <x:v>868</x:v>
       </x:c>
-      <x:c r="F60" s="18" t="s">
+      <x:c r="H60" s="19" t="s">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="I60" s="19" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="J60" s="18" t="s">
         <x:v>869</x:v>
-      </x:c>
-      <x:c r="G60" s="18" t="s">
-        <x:v>870</x:v>
-      </x:c>
-      <x:c r="H60" s="19" t="s">
-        <x:v>628</x:v>
-      </x:c>
-      <x:c r="I60" s="19" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="J60" s="18" t="s">
-        <x:v>871</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="55" customHeight="1">
@@ -10267,31 +10507,31 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="B61" s="24" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C61" s="46" t="s">
+        <x:v>870</x:v>
+      </x:c>
+      <x:c r="D61" s="19" t="s">
+        <x:v>871</x:v>
+      </x:c>
+      <x:c r="E61" s="18" t="s">
         <x:v>872</x:v>
       </x:c>
-      <x:c r="D61" s="19" t="s">
+      <x:c r="F61" s="18" t="s">
         <x:v>873</x:v>
       </x:c>
-      <x:c r="E61" s="18" t="s">
+      <x:c r="G61" s="18" t="s">
         <x:v>874</x:v>
-      </x:c>
-      <x:c r="F61" s="18" t="s">
-        <x:v>875</x:v>
-      </x:c>
-      <x:c r="G61" s="18" t="s">
-        <x:v>876</x:v>
       </x:c>
       <x:c r="H61" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I61" s="19" t="s">
-        <x:v>877</x:v>
+        <x:v>875</x:v>
       </x:c>
       <x:c r="J61" s="18" t="s">
-        <x:v>878</x:v>
+        <x:v>876</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="55" customHeight="1">
@@ -10299,31 +10539,31 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="B62" s="24" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C62" s="46" t="s">
+        <x:v>877</x:v>
+      </x:c>
+      <x:c r="D62" s="19" t="s">
+        <x:v>878</x:v>
+      </x:c>
+      <x:c r="E62" s="18" t="s">
         <x:v>879</x:v>
       </x:c>
-      <x:c r="D62" s="19" t="s">
+      <x:c r="F62" s="18" t="s">
         <x:v>880</x:v>
       </x:c>
-      <x:c r="E62" s="18" t="s">
+      <x:c r="G62" s="18" t="s">
         <x:v>881</x:v>
-      </x:c>
-      <x:c r="F62" s="18" t="s">
-        <x:v>882</x:v>
-      </x:c>
-      <x:c r="G62" s="18" t="s">
-        <x:v>883</x:v>
       </x:c>
       <x:c r="H62" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I62" s="19" t="s">
-        <x:v>884</x:v>
+        <x:v>882</x:v>
       </x:c>
       <x:c r="J62" s="18" t="s">
-        <x:v>885</x:v>
+        <x:v>883</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="55" customHeight="1">
@@ -10331,31 +10571,31 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="B63" s="24" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C63" s="46" t="s">
+        <x:v>884</x:v>
+      </x:c>
+      <x:c r="D63" s="19" t="s">
+        <x:v>885</x:v>
+      </x:c>
+      <x:c r="E63" s="18" t="s">
         <x:v>886</x:v>
       </x:c>
-      <x:c r="D63" s="19" t="s">
+      <x:c r="F63" s="18" t="s">
         <x:v>887</x:v>
       </x:c>
-      <x:c r="E63" s="18" t="s">
-        <x:v>888</x:v>
-      </x:c>
-      <x:c r="F63" s="18" t="s">
-        <x:v>889</x:v>
-      </x:c>
       <x:c r="G63" s="18" t="s">
-        <x:v>883</x:v>
+        <x:v>881</x:v>
       </x:c>
       <x:c r="H63" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I63" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J63" s="18" t="s">
-        <x:v>890</x:v>
+        <x:v>888</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="55" customHeight="1">
@@ -10363,31 +10603,31 @@
         <x:v>59</x:v>
       </x:c>
       <x:c r="B64" s="24" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C64" s="46" t="s">
+        <x:v>889</x:v>
+      </x:c>
+      <x:c r="D64" s="19" t="s">
+        <x:v>890</x:v>
+      </x:c>
+      <x:c r="E64" s="18" t="s">
         <x:v>891</x:v>
       </x:c>
-      <x:c r="D64" s="19" t="s">
+      <x:c r="F64" s="18" t="s">
         <x:v>892</x:v>
       </x:c>
-      <x:c r="E64" s="18" t="s">
-        <x:v>893</x:v>
-      </x:c>
-      <x:c r="F64" s="18" t="s">
-        <x:v>894</x:v>
-      </x:c>
       <x:c r="G64" s="18" t="s">
-        <x:v>842</x:v>
+        <x:v>840</x:v>
       </x:c>
       <x:c r="H64" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I64" s="19" t="s">
-        <x:v>895</x:v>
+        <x:v>893</x:v>
       </x:c>
       <x:c r="J64" s="18" t="s">
-        <x:v>896</x:v>
+        <x:v>894</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="55" customHeight="1">
@@ -10395,31 +10635,31 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="B65" s="24" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C65" s="46" t="s">
+        <x:v>895</x:v>
+      </x:c>
+      <x:c r="D65" s="19" t="s">
+        <x:v>896</x:v>
+      </x:c>
+      <x:c r="E65" s="18" t="s">
         <x:v>897</x:v>
       </x:c>
-      <x:c r="D65" s="19" t="s">
+      <x:c r="F65" s="18" t="s">
         <x:v>898</x:v>
       </x:c>
-      <x:c r="E65" s="18" t="s">
+      <x:c r="G65" s="18" t="s">
+        <x:v>840</x:v>
+      </x:c>
+      <x:c r="H65" s="19" t="s">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="I65" s="19" t="s">
+        <x:v>713</x:v>
+      </x:c>
+      <x:c r="J65" s="18" t="s">
         <x:v>899</x:v>
-      </x:c>
-      <x:c r="F65" s="18" t="s">
-        <x:v>900</x:v>
-      </x:c>
-      <x:c r="G65" s="18" t="s">
-        <x:v>842</x:v>
-      </x:c>
-      <x:c r="H65" s="19" t="s">
-        <x:v>628</x:v>
-      </x:c>
-      <x:c r="I65" s="19" t="s">
-        <x:v>715</x:v>
-      </x:c>
-      <x:c r="J65" s="18" t="s">
-        <x:v>901</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="55" customHeight="1">
@@ -10427,31 +10667,31 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="B66" s="24" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C66" s="46" t="s">
+        <x:v>900</x:v>
+      </x:c>
+      <x:c r="D66" s="19" t="s">
+        <x:v>901</x:v>
+      </x:c>
+      <x:c r="E66" s="18" t="s">
         <x:v>902</x:v>
       </x:c>
-      <x:c r="D66" s="19" t="s">
+      <x:c r="F66" s="18" t="s">
         <x:v>903</x:v>
       </x:c>
-      <x:c r="E66" s="18" t="s">
+      <x:c r="G66" s="18" t="s">
         <x:v>904</x:v>
       </x:c>
-      <x:c r="F66" s="18" t="s">
+      <x:c r="H66" s="19" t="s">
         <x:v>905</x:v>
       </x:c>
-      <x:c r="G66" s="18" t="s">
+      <x:c r="I66" s="19" t="s">
+        <x:v>713</x:v>
+      </x:c>
+      <x:c r="J66" s="18" t="s">
         <x:v>906</x:v>
-      </x:c>
-      <x:c r="H66" s="19" t="s">
-        <x:v>907</x:v>
-      </x:c>
-      <x:c r="I66" s="19" t="s">
-        <x:v>715</x:v>
-      </x:c>
-      <x:c r="J66" s="18" t="s">
-        <x:v>908</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="55" customHeight="1">
@@ -10459,31 +10699,31 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="B67" s="24" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C67" s="46" t="s">
+        <x:v>907</x:v>
+      </x:c>
+      <x:c r="D67" s="19" t="s">
+        <x:v>908</x:v>
+      </x:c>
+      <x:c r="E67" s="18" t="s">
         <x:v>909</x:v>
       </x:c>
-      <x:c r="D67" s="19" t="s">
+      <x:c r="F67" s="18" t="s">
         <x:v>910</x:v>
       </x:c>
-      <x:c r="E67" s="18" t="s">
+      <x:c r="G67" s="18" t="s">
+        <x:v>904</x:v>
+      </x:c>
+      <x:c r="H67" s="19" t="s">
+        <x:v>905</x:v>
+      </x:c>
+      <x:c r="I67" s="19" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="J67" s="18" t="s">
         <x:v>911</x:v>
-      </x:c>
-      <x:c r="F67" s="18" t="s">
-        <x:v>912</x:v>
-      </x:c>
-      <x:c r="G67" s="18" t="s">
-        <x:v>906</x:v>
-      </x:c>
-      <x:c r="H67" s="19" t="s">
-        <x:v>907</x:v>
-      </x:c>
-      <x:c r="I67" s="19" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="J67" s="18" t="s">
-        <x:v>913</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="55" customHeight="1">
@@ -10491,31 +10731,31 @@
         <x:v>63</x:v>
       </x:c>
       <x:c r="B68" s="24" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C68" s="46" t="s">
+        <x:v>912</x:v>
+      </x:c>
+      <x:c r="D68" s="19" t="s">
+        <x:v>913</x:v>
+      </x:c>
+      <x:c r="E68" s="18" t="s">
         <x:v>914</x:v>
       </x:c>
-      <x:c r="D68" s="19" t="s">
+      <x:c r="F68" s="18" t="s">
         <x:v>915</x:v>
       </x:c>
-      <x:c r="E68" s="18" t="s">
+      <x:c r="G68" s="18" t="str">
+        <x:v>P00/P01–P11/D04</x:v>
+      </x:c>
+      <x:c r="H68" s="19" t="s">
         <x:v>916</x:v>
       </x:c>
-      <x:c r="F68" s="18" t="s">
+      <x:c r="I68" s="19" t="s">
+        <x:v>713</x:v>
+      </x:c>
+      <x:c r="J68" s="18" t="s">
         <x:v>917</x:v>
-      </x:c>
-      <x:c r="G68" s="18" t="s">
-        <x:v>918</x:v>
-      </x:c>
-      <x:c r="H68" s="19" t="s">
-        <x:v>919</x:v>
-      </x:c>
-      <x:c r="I68" s="19" t="s">
-        <x:v>715</x:v>
-      </x:c>
-      <x:c r="J68" s="18" t="s">
-        <x:v>920</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="55" customHeight="1">
@@ -10523,31 +10763,31 @@
         <x:v>64</x:v>
       </x:c>
       <x:c r="B69" s="24" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C69" s="46" t="s">
+        <x:v>918</x:v>
+      </x:c>
+      <x:c r="D69" s="19" t="s">
+        <x:v>919</x:v>
+      </x:c>
+      <x:c r="E69" s="18" t="s">
+        <x:v>920</x:v>
+      </x:c>
+      <x:c r="F69" s="18" t="s">
         <x:v>921</x:v>
       </x:c>
-      <x:c r="D69" s="19" t="s">
-        <x:v>922</x:v>
-      </x:c>
-      <x:c r="E69" s="18" t="s">
-        <x:v>923</x:v>
-      </x:c>
-      <x:c r="F69" s="18" t="s">
-        <x:v>924</x:v>
-      </x:c>
       <x:c r="G69" s="18" t="str">
-        <x:v>P00/P01–P09/D04</x:v>
+        <x:v>P00/P01–P11/D04</x:v>
       </x:c>
       <x:c r="H69" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I69" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J69" s="18" t="s">
-        <x:v>925</x:v>
+        <x:v>922</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="55" customHeight="1">
@@ -10555,31 +10795,31 @@
         <x:v>65</x:v>
       </x:c>
       <x:c r="B70" s="24" t="s">
-        <x:v>837</x:v>
+        <x:v>835</x:v>
       </x:c>
       <x:c r="C70" s="46" t="s">
+        <x:v>923</x:v>
+      </x:c>
+      <x:c r="D70" s="19" t="s">
+        <x:v>924</x:v>
+      </x:c>
+      <x:c r="E70" s="18" t="s">
+        <x:v>925</x:v>
+      </x:c>
+      <x:c r="F70" s="18" t="s">
         <x:v>926</x:v>
       </x:c>
-      <x:c r="D70" s="19" t="s">
-        <x:v>927</x:v>
-      </x:c>
-      <x:c r="E70" s="18" t="s">
-        <x:v>928</x:v>
-      </x:c>
-      <x:c r="F70" s="18" t="s">
-        <x:v>929</x:v>
-      </x:c>
       <x:c r="G70" s="18" t="s">
-        <x:v>870</x:v>
+        <x:v>868</x:v>
       </x:c>
       <x:c r="H70" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I70" s="19" t="s">
-        <x:v>930</x:v>
+        <x:v>927</x:v>
       </x:c>
       <x:c r="J70" s="18" t="s">
-        <x:v>931</x:v>
+        <x:v>928</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="55" customHeight="1">
@@ -10587,31 +10827,31 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="B71" s="44" t="s">
+        <x:v>929</x:v>
+      </x:c>
+      <x:c r="C71" s="46" t="s">
+        <x:v>930</x:v>
+      </x:c>
+      <x:c r="D71" s="19" t="s">
+        <x:v>931</x:v>
+      </x:c>
+      <x:c r="E71" s="18" t="s">
         <x:v>932</x:v>
       </x:c>
-      <x:c r="C71" s="46" t="s">
+      <x:c r="F71" s="18" t="s">
         <x:v>933</x:v>
       </x:c>
-      <x:c r="D71" s="19" t="s">
+      <x:c r="G71" s="18" t="s">
         <x:v>934</x:v>
-      </x:c>
-      <x:c r="E71" s="18" t="s">
-        <x:v>935</x:v>
-      </x:c>
-      <x:c r="F71" s="18" t="s">
-        <x:v>936</x:v>
-      </x:c>
-      <x:c r="G71" s="18" t="s">
-        <x:v>937</x:v>
       </x:c>
       <x:c r="H71" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I71" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J71" s="18" t="s">
-        <x:v>938</x:v>
+        <x:v>935</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="55" customHeight="1">
@@ -10619,31 +10859,31 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="B72" s="44" t="s">
-        <x:v>932</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="C72" s="46" t="s">
+        <x:v>936</x:v>
+      </x:c>
+      <x:c r="D72" s="19" t="s">
+        <x:v>937</x:v>
+      </x:c>
+      <x:c r="E72" s="18" t="s">
+        <x:v>938</x:v>
+      </x:c>
+      <x:c r="F72" s="18" t="s">
         <x:v>939</x:v>
       </x:c>
-      <x:c r="D72" s="19" t="s">
+      <x:c r="G72" s="18" t="s">
         <x:v>940</x:v>
-      </x:c>
-      <x:c r="E72" s="18" t="s">
-        <x:v>941</x:v>
-      </x:c>
-      <x:c r="F72" s="18" t="s">
-        <x:v>942</x:v>
-      </x:c>
-      <x:c r="G72" s="18" t="s">
-        <x:v>943</x:v>
       </x:c>
       <x:c r="H72" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I72" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J72" s="18" t="s">
-        <x:v>944</x:v>
+        <x:v>941</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="55" customHeight="1">
@@ -10651,31 +10891,31 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="B73" s="44" t="s">
-        <x:v>932</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="C73" s="46" t="s">
+        <x:v>942</x:v>
+      </x:c>
+      <x:c r="D73" s="19" t="s">
+        <x:v>943</x:v>
+      </x:c>
+      <x:c r="E73" s="18" t="s">
+        <x:v>944</x:v>
+      </x:c>
+      <x:c r="F73" s="18" t="s">
         <x:v>945</x:v>
       </x:c>
-      <x:c r="D73" s="19" t="s">
-        <x:v>946</x:v>
-      </x:c>
-      <x:c r="E73" s="18" t="s">
-        <x:v>947</x:v>
-      </x:c>
-      <x:c r="F73" s="18" t="s">
-        <x:v>948</x:v>
-      </x:c>
       <x:c r="G73" s="18" t="s">
-        <x:v>943</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="H73" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I73" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J73" s="18" t="s">
-        <x:v>949</x:v>
+        <x:v>946</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="55" customHeight="1">
@@ -10683,31 +10923,31 @@
         <x:v>69</x:v>
       </x:c>
       <x:c r="B74" s="44" t="s">
-        <x:v>932</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="C74" s="46" t="s">
+        <x:v>947</x:v>
+      </x:c>
+      <x:c r="D74" s="19" t="s">
+        <x:v>948</x:v>
+      </x:c>
+      <x:c r="E74" s="18" t="s">
+        <x:v>949</x:v>
+      </x:c>
+      <x:c r="F74" s="18" t="s">
         <x:v>950</x:v>
       </x:c>
-      <x:c r="D74" s="19" t="s">
+      <x:c r="G74" s="18" t="s">
         <x:v>951</x:v>
       </x:c>
-      <x:c r="E74" s="18" t="s">
+      <x:c r="H74" s="19" t="s">
         <x:v>952</x:v>
       </x:c>
-      <x:c r="F74" s="18" t="s">
+      <x:c r="I74" s="19" t="s">
+        <x:v>713</x:v>
+      </x:c>
+      <x:c r="J74" s="18" t="s">
         <x:v>953</x:v>
-      </x:c>
-      <x:c r="G74" s="18" t="s">
-        <x:v>954</x:v>
-      </x:c>
-      <x:c r="H74" s="19" t="s">
-        <x:v>955</x:v>
-      </x:c>
-      <x:c r="I74" s="19" t="s">
-        <x:v>715</x:v>
-      </x:c>
-      <x:c r="J74" s="18" t="s">
-        <x:v>956</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="55" customHeight="1">
@@ -10715,31 +10955,31 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="B75" s="44" t="s">
-        <x:v>932</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="C75" s="46" t="s">
+        <x:v>954</x:v>
+      </x:c>
+      <x:c r="D75" s="19" t="s">
+        <x:v>955</x:v>
+      </x:c>
+      <x:c r="E75" s="18" t="s">
+        <x:v>956</x:v>
+      </x:c>
+      <x:c r="F75" s="18" t="s">
         <x:v>957</x:v>
       </x:c>
-      <x:c r="D75" s="19" t="s">
-        <x:v>958</x:v>
-      </x:c>
-      <x:c r="E75" s="18" t="s">
-        <x:v>959</x:v>
-      </x:c>
-      <x:c r="F75" s="18" t="s">
-        <x:v>960</x:v>
-      </x:c>
       <x:c r="G75" s="18" t="s">
-        <x:v>943</x:v>
+        <x:v>940</x:v>
       </x:c>
       <x:c r="H75" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I75" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J75" s="18" t="s">
-        <x:v>961</x:v>
+        <x:v>958</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="55" customHeight="1">
@@ -10747,31 +10987,31 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="B76" s="44" t="s">
-        <x:v>932</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="C76" s="46" t="s">
+        <x:v>959</x:v>
+      </x:c>
+      <x:c r="D76" s="19" t="s">
+        <x:v>960</x:v>
+      </x:c>
+      <x:c r="E76" s="18" t="s">
+        <x:v>961</x:v>
+      </x:c>
+      <x:c r="F76" s="18" t="s">
         <x:v>962</x:v>
       </x:c>
-      <x:c r="D76" s="19" t="s">
-        <x:v>963</x:v>
-      </x:c>
-      <x:c r="E76" s="18" t="s">
-        <x:v>964</x:v>
-      </x:c>
-      <x:c r="F76" s="18" t="s">
-        <x:v>965</x:v>
-      </x:c>
       <x:c r="G76" s="18" t="s">
-        <x:v>803</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="H76" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I76" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J76" s="18" t="s">
-        <x:v>966</x:v>
+        <x:v>963</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="55" customHeight="1">
@@ -10779,31 +11019,31 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="B77" s="44" t="s">
-        <x:v>932</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="C77" s="46" t="s">
+        <x:v>964</x:v>
+      </x:c>
+      <x:c r="D77" s="19" t="s">
+        <x:v>965</x:v>
+      </x:c>
+      <x:c r="E77" s="18" t="s">
+        <x:v>966</x:v>
+      </x:c>
+      <x:c r="F77" s="18" t="s">
         <x:v>967</x:v>
       </x:c>
-      <x:c r="D77" s="19" t="s">
+      <x:c r="G77" s="18" t="s">
         <x:v>968</x:v>
-      </x:c>
-      <x:c r="E77" s="18" t="s">
-        <x:v>969</x:v>
-      </x:c>
-      <x:c r="F77" s="18" t="s">
-        <x:v>970</x:v>
-      </x:c>
-      <x:c r="G77" s="18" t="s">
-        <x:v>971</x:v>
       </x:c>
       <x:c r="H77" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I77" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J77" s="18" t="s">
-        <x:v>972</x:v>
+        <x:v>969</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="55" customHeight="1">
@@ -10811,31 +11051,31 @@
         <x:v>73</x:v>
       </x:c>
       <x:c r="B78" s="44" t="s">
-        <x:v>932</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="C78" s="46" t="s">
+        <x:v>970</x:v>
+      </x:c>
+      <x:c r="D78" s="19" t="s">
+        <x:v>971</x:v>
+      </x:c>
+      <x:c r="E78" s="18" t="s">
+        <x:v>972</x:v>
+      </x:c>
+      <x:c r="F78" s="18" t="s">
         <x:v>973</x:v>
       </x:c>
-      <x:c r="D78" s="19" t="s">
+      <x:c r="G78" s="18" t="s">
         <x:v>974</x:v>
-      </x:c>
-      <x:c r="E78" s="18" t="s">
-        <x:v>975</x:v>
-      </x:c>
-      <x:c r="F78" s="18" t="s">
-        <x:v>976</x:v>
-      </x:c>
-      <x:c r="G78" s="18" t="s">
-        <x:v>977</x:v>
       </x:c>
       <x:c r="H78" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I78" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J78" s="18" t="s">
-        <x:v>978</x:v>
+        <x:v>975</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="55" customHeight="1">
@@ -10843,31 +11083,31 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="B79" s="44" t="s">
-        <x:v>932</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="C79" s="46" t="s">
+        <x:v>976</x:v>
+      </x:c>
+      <x:c r="D79" s="19" t="s">
+        <x:v>977</x:v>
+      </x:c>
+      <x:c r="E79" s="18" t="s">
+        <x:v>978</x:v>
+      </x:c>
+      <x:c r="F79" s="18" t="s">
         <x:v>979</x:v>
       </x:c>
-      <x:c r="D79" s="19" t="s">
+      <x:c r="G79" s="18" t="s">
         <x:v>980</x:v>
-      </x:c>
-      <x:c r="E79" s="18" t="s">
-        <x:v>981</x:v>
-      </x:c>
-      <x:c r="F79" s="18" t="s">
-        <x:v>982</x:v>
-      </x:c>
-      <x:c r="G79" s="18" t="s">
-        <x:v>983</x:v>
       </x:c>
       <x:c r="H79" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I79" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J79" s="18" t="s">
-        <x:v>984</x:v>
+        <x:v>981</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="55" customHeight="1">
@@ -10875,31 +11115,31 @@
         <x:v>75</x:v>
       </x:c>
       <x:c r="B80" s="44" t="s">
-        <x:v>932</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="C80" s="46" t="s">
+        <x:v>982</x:v>
+      </x:c>
+      <x:c r="D80" s="19" t="s">
+        <x:v>983</x:v>
+      </x:c>
+      <x:c r="E80" s="18" t="s">
+        <x:v>984</x:v>
+      </x:c>
+      <x:c r="F80" s="18" t="s">
         <x:v>985</x:v>
       </x:c>
-      <x:c r="D80" s="19" t="s">
+      <x:c r="G80" s="18" t="s">
         <x:v>986</x:v>
-      </x:c>
-      <x:c r="E80" s="18" t="s">
-        <x:v>987</x:v>
-      </x:c>
-      <x:c r="F80" s="18" t="s">
-        <x:v>988</x:v>
-      </x:c>
-      <x:c r="G80" s="18" t="s">
-        <x:v>989</x:v>
       </x:c>
       <x:c r="H80" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I80" s="19" t="s">
-        <x:v>990</x:v>
+        <x:v>987</x:v>
       </x:c>
       <x:c r="J80" s="18" t="s">
-        <x:v>991</x:v>
+        <x:v>988</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="55" customHeight="1">
@@ -10907,31 +11147,31 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="B81" s="44" t="s">
-        <x:v>932</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="C81" s="46" t="s">
+        <x:v>989</x:v>
+      </x:c>
+      <x:c r="D81" s="19" t="s">
+        <x:v>990</x:v>
+      </x:c>
+      <x:c r="E81" s="18" t="s">
+        <x:v>991</x:v>
+      </x:c>
+      <x:c r="F81" s="18" t="s">
         <x:v>992</x:v>
       </x:c>
-      <x:c r="D81" s="19" t="s">
-        <x:v>993</x:v>
-      </x:c>
-      <x:c r="E81" s="18" t="s">
-        <x:v>994</x:v>
-      </x:c>
-      <x:c r="F81" s="18" t="s">
-        <x:v>995</x:v>
-      </x:c>
       <x:c r="G81" s="18" t="s">
-        <x:v>989</x:v>
+        <x:v>986</x:v>
       </x:c>
       <x:c r="H81" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I81" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J81" s="18" t="s">
-        <x:v>996</x:v>
+        <x:v>993</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="55" customHeight="1">
@@ -10939,31 +11179,31 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="B82" s="44" t="s">
-        <x:v>932</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="C82" s="46" t="s">
+        <x:v>994</x:v>
+      </x:c>
+      <x:c r="D82" s="19" t="s">
+        <x:v>995</x:v>
+      </x:c>
+      <x:c r="E82" s="18" t="s">
+        <x:v>996</x:v>
+      </x:c>
+      <x:c r="F82" s="18" t="s">
         <x:v>997</x:v>
       </x:c>
-      <x:c r="D82" s="19" t="s">
+      <x:c r="G82" s="18" t="s">
         <x:v>998</x:v>
-      </x:c>
-      <x:c r="E82" s="18" t="s">
-        <x:v>999</x:v>
-      </x:c>
-      <x:c r="F82" s="18" t="s">
-        <x:v>1000</x:v>
-      </x:c>
-      <x:c r="G82" s="18" t="s">
-        <x:v>1001</x:v>
       </x:c>
       <x:c r="H82" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I82" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J82" s="18" t="s">
-        <x:v>1002</x:v>
+        <x:v>999</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="55" customHeight="1">
@@ -10971,31 +11211,31 @@
         <x:v>78</x:v>
       </x:c>
       <x:c r="B83" s="44" t="s">
-        <x:v>932</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="C83" s="46" t="s">
+        <x:v>1000</x:v>
+      </x:c>
+      <x:c r="D83" s="19" t="s">
+        <x:v>1001</x:v>
+      </x:c>
+      <x:c r="E83" s="18" t="s">
+        <x:v>1002</x:v>
+      </x:c>
+      <x:c r="F83" s="18" t="s">
         <x:v>1003</x:v>
       </x:c>
-      <x:c r="D83" s="19" t="s">
+      <x:c r="G83" s="18" t="s">
         <x:v>1004</x:v>
-      </x:c>
-      <x:c r="E83" s="18" t="s">
-        <x:v>1005</x:v>
-      </x:c>
-      <x:c r="F83" s="18" t="s">
-        <x:v>1006</x:v>
-      </x:c>
-      <x:c r="G83" s="18" t="s">
-        <x:v>1007</x:v>
       </x:c>
       <x:c r="H83" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I83" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J83" s="18" t="s">
-        <x:v>1008</x:v>
+        <x:v>1005</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="55" customHeight="1">
@@ -11003,31 +11243,31 @@
         <x:v>79</x:v>
       </x:c>
       <x:c r="B84" s="44" t="s">
-        <x:v>932</x:v>
+        <x:v>929</x:v>
       </x:c>
       <x:c r="C84" s="46" t="s">
+        <x:v>1006</x:v>
+      </x:c>
+      <x:c r="D84" s="19" t="s">
+        <x:v>1007</x:v>
+      </x:c>
+      <x:c r="E84" s="18" t="s">
+        <x:v>1008</x:v>
+      </x:c>
+      <x:c r="F84" s="18" t="s">
         <x:v>1009</x:v>
       </x:c>
-      <x:c r="D84" s="19" t="s">
+      <x:c r="G84" s="18" t="s">
         <x:v>1010</x:v>
-      </x:c>
-      <x:c r="E84" s="18" t="s">
-        <x:v>1011</x:v>
-      </x:c>
-      <x:c r="F84" s="18" t="s">
-        <x:v>1012</x:v>
-      </x:c>
-      <x:c r="G84" s="18" t="s">
-        <x:v>1013</x:v>
       </x:c>
       <x:c r="H84" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I84" s="19" t="s">
-        <x:v>715</x:v>
+        <x:v>713</x:v>
       </x:c>
       <x:c r="J84" s="18" t="s">
-        <x:v>1014</x:v>
+        <x:v>1011</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="55" customHeight="1">
@@ -11035,31 +11275,31 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="B85" s="49" t="s">
+        <x:v>1012</x:v>
+      </x:c>
+      <x:c r="C85" s="46" t="s">
+        <x:v>1013</x:v>
+      </x:c>
+      <x:c r="D85" s="19" t="s">
+        <x:v>896</x:v>
+      </x:c>
+      <x:c r="E85" s="18" t="s">
+        <x:v>1014</x:v>
+      </x:c>
+      <x:c r="F85" s="18" t="s">
         <x:v>1015</x:v>
       </x:c>
-      <x:c r="C85" s="46" t="s">
+      <x:c r="G85" s="18" t="s">
         <x:v>1016</x:v>
-      </x:c>
-      <x:c r="D85" s="19" t="s">
-        <x:v>898</x:v>
-      </x:c>
-      <x:c r="E85" s="18" t="s">
-        <x:v>1017</x:v>
-      </x:c>
-      <x:c r="F85" s="18" t="s">
-        <x:v>1018</x:v>
-      </x:c>
-      <x:c r="G85" s="18" t="s">
-        <x:v>1019</x:v>
       </x:c>
       <x:c r="H85" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I85" s="19" t="s">
-        <x:v>613</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="J85" s="18" t="s">
-        <x:v>1020</x:v>
+        <x:v>1017</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="55" customHeight="1">
@@ -11067,31 +11307,31 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="B86" s="49" t="s">
-        <x:v>1015</x:v>
+        <x:v>1012</x:v>
       </x:c>
       <x:c r="C86" s="46" t="s">
+        <x:v>1018</x:v>
+      </x:c>
+      <x:c r="D86" s="19" t="s">
+        <x:v>1019</x:v>
+      </x:c>
+      <x:c r="E86" s="18" t="s">
+        <x:v>1020</x:v>
+      </x:c>
+      <x:c r="F86" s="18" t="s">
         <x:v>1021</x:v>
       </x:c>
-      <x:c r="D86" s="19" t="s">
+      <x:c r="G86" s="18" t="s">
         <x:v>1022</x:v>
-      </x:c>
-      <x:c r="E86" s="18" t="s">
-        <x:v>1023</x:v>
-      </x:c>
-      <x:c r="F86" s="18" t="s">
-        <x:v>1024</x:v>
-      </x:c>
-      <x:c r="G86" s="18" t="s">
-        <x:v>1025</x:v>
       </x:c>
       <x:c r="H86" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I86" s="19" t="s">
-        <x:v>1026</x:v>
+        <x:v>1023</x:v>
       </x:c>
       <x:c r="J86" s="18" t="s">
-        <x:v>1027</x:v>
+        <x:v>1024</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="55" customHeight="1">
@@ -11099,31 +11339,31 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="B87" s="49" t="s">
-        <x:v>1015</x:v>
+        <x:v>1012</x:v>
       </x:c>
       <x:c r="C87" s="46" t="s">
+        <x:v>1025</x:v>
+      </x:c>
+      <x:c r="D87" s="19" t="s">
+        <x:v>1026</x:v>
+      </x:c>
+      <x:c r="E87" s="18" t="s">
+        <x:v>1027</x:v>
+      </x:c>
+      <x:c r="F87" s="18" t="s">
+        <x:v>1021</x:v>
+      </x:c>
+      <x:c r="G87" s="18" t="s">
         <x:v>1028</x:v>
       </x:c>
-      <x:c r="D87" s="19" t="s">
+      <x:c r="H87" s="47" t="s">
         <x:v>1029</x:v>
       </x:c>
-      <x:c r="E87" s="18" t="s">
+      <x:c r="I87" s="19" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="J87" s="18" t="s">
         <x:v>1030</x:v>
-      </x:c>
-      <x:c r="F87" s="18" t="s">
-        <x:v>1024</x:v>
-      </x:c>
-      <x:c r="G87" s="18" t="s">
-        <x:v>1031</x:v>
-      </x:c>
-      <x:c r="H87" s="47" t="s">
-        <x:v>1032</x:v>
-      </x:c>
-      <x:c r="I87" s="19" t="s">
-        <x:v>613</x:v>
-      </x:c>
-      <x:c r="J87" s="18" t="s">
-        <x:v>1033</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="55" customHeight="1">
@@ -11131,31 +11371,31 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="B88" s="49" t="s">
-        <x:v>1015</x:v>
+        <x:v>1012</x:v>
       </x:c>
       <x:c r="C88" s="46" t="s">
-        <x:v>1034</x:v>
+        <x:v>1031</x:v>
       </x:c>
       <x:c r="D88" s="19" t="s">
-        <x:v>1035</x:v>
+        <x:v>1032</x:v>
       </x:c>
       <x:c r="E88" s="18" t="s">
         <x:v>91</x:v>
       </x:c>
       <x:c r="F88" s="18" t="s">
-        <x:v>1036</x:v>
+        <x:v>1033</x:v>
       </x:c>
       <x:c r="G88" s="18" t="s">
-        <x:v>1037</x:v>
+        <x:v>1034</x:v>
       </x:c>
       <x:c r="H88" s="47" t="s">
-        <x:v>1032</x:v>
+        <x:v>1029</x:v>
       </x:c>
       <x:c r="I88" s="19" t="s">
-        <x:v>732</x:v>
+        <x:v>730</x:v>
       </x:c>
       <x:c r="J88" s="18" t="s">
-        <x:v>1038</x:v>
+        <x:v>1035</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="55" customHeight="1">
@@ -11163,31 +11403,31 @@
         <x:v>84</x:v>
       </x:c>
       <x:c r="B89" s="49" t="s">
-        <x:v>1015</x:v>
+        <x:v>1012</x:v>
       </x:c>
       <x:c r="C89" s="46" t="s">
-        <x:v>1039</x:v>
+        <x:v>1036</x:v>
       </x:c>
       <x:c r="D89" s="19" t="s">
-        <x:v>1040</x:v>
+        <x:v>1037</x:v>
       </x:c>
       <x:c r="E89" s="18" t="s">
-        <x:v>1041</x:v>
+        <x:v>1038</x:v>
       </x:c>
       <x:c r="F89" s="18" t="s">
-        <x:v>1024</x:v>
+        <x:v>1021</x:v>
       </x:c>
       <x:c r="G89" s="18" t="s">
-        <x:v>1025</x:v>
+        <x:v>1022</x:v>
       </x:c>
       <x:c r="H89" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I89" s="19" t="s">
-        <x:v>1042</x:v>
+        <x:v>1039</x:v>
       </x:c>
       <x:c r="J89" s="18" t="s">
-        <x:v>1043</x:v>
+        <x:v>1040</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="55" customHeight="1">
@@ -11195,31 +11435,31 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="B90" s="49" t="s">
-        <x:v>1015</x:v>
+        <x:v>1012</x:v>
       </x:c>
       <x:c r="C90" s="46" t="s">
+        <x:v>1041</x:v>
+      </x:c>
+      <x:c r="D90" s="19" t="s">
+        <x:v>1042</x:v>
+      </x:c>
+      <x:c r="E90" s="18" t="s">
+        <x:v>1043</x:v>
+      </x:c>
+      <x:c r="F90" s="18" t="s">
         <x:v>1044</x:v>
       </x:c>
-      <x:c r="D90" s="19" t="s">
+      <x:c r="G90" s="18" t="s">
         <x:v>1045</x:v>
       </x:c>
-      <x:c r="E90" s="18" t="s">
+      <x:c r="H90" s="47" t="s">
+        <x:v>1029</x:v>
+      </x:c>
+      <x:c r="I90" s="19" t="s">
+        <x:v>713</x:v>
+      </x:c>
+      <x:c r="J90" s="18" t="s">
         <x:v>1046</x:v>
-      </x:c>
-      <x:c r="F90" s="18" t="s">
-        <x:v>1047</x:v>
-      </x:c>
-      <x:c r="G90" s="18" t="s">
-        <x:v>1048</x:v>
-      </x:c>
-      <x:c r="H90" s="47" t="s">
-        <x:v>1032</x:v>
-      </x:c>
-      <x:c r="I90" s="19" t="s">
-        <x:v>715</x:v>
-      </x:c>
-      <x:c r="J90" s="18" t="s">
-        <x:v>1049</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="55" customHeight="1">
@@ -11227,31 +11467,31 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="B91" s="49" t="s">
-        <x:v>1015</x:v>
+        <x:v>1012</x:v>
       </x:c>
       <x:c r="C91" s="46" t="s">
+        <x:v>1047</x:v>
+      </x:c>
+      <x:c r="D91" s="19" t="s">
+        <x:v>1048</x:v>
+      </x:c>
+      <x:c r="E91" s="18" t="s">
+        <x:v>1049</x:v>
+      </x:c>
+      <x:c r="F91" s="18" t="s">
         <x:v>1050</x:v>
       </x:c>
-      <x:c r="D91" s="19" t="s">
+      <x:c r="G91" s="18" t="s">
         <x:v>1051</x:v>
-      </x:c>
-      <x:c r="E91" s="18" t="s">
-        <x:v>1052</x:v>
-      </x:c>
-      <x:c r="F91" s="18" t="s">
-        <x:v>1053</x:v>
-      </x:c>
-      <x:c r="G91" s="18" t="s">
-        <x:v>1054</x:v>
       </x:c>
       <x:c r="H91" s="19" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="I91" s="19" t="s">
-        <x:v>828</x:v>
+        <x:v>826</x:v>
       </x:c>
       <x:c r="J91" s="18" t="s">
-        <x:v>1055</x:v>
+        <x:v>1052</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="55" customHeight="1">
@@ -11259,31 +11499,128 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="B92" s="49" t="s">
-        <x:v>1015</x:v>
+        <x:v>1012</x:v>
       </x:c>
       <x:c r="C92" s="46" t="s">
+        <x:v>1053</x:v>
+      </x:c>
+      <x:c r="D92" s="19" t="s">
+        <x:v>1054</x:v>
+      </x:c>
+      <x:c r="E92" s="18" t="s">
+        <x:v>1055</x:v>
+      </x:c>
+      <x:c r="F92" s="18" t="s">
         <x:v>1056</x:v>
       </x:c>
-      <x:c r="D92" s="19" t="s">
+      <x:c r="G92" s="18" t="s">
         <x:v>1057</x:v>
       </x:c>
-      <x:c r="E92" s="18" t="s">
+      <x:c r="H92" s="19" t="s">
+        <x:v>1057</x:v>
+      </x:c>
+      <x:c r="I92" s="19" t="s">
         <x:v>1058</x:v>
       </x:c>
-      <x:c r="F92" s="18" t="s">
+      <x:c r="J92" s="18" t="s">
         <x:v>1059</x:v>
       </x:c>
-      <x:c r="G92" s="18" t="s">
-        <x:v>1060</x:v>
-      </x:c>
-      <x:c r="H92" s="19" t="s">
-        <x:v>1060</x:v>
-      </x:c>
-      <x:c r="I92" s="19" t="s">
-        <x:v>1061</x:v>
-      </x:c>
-      <x:c r="J92" s="18" t="s">
-        <x:v>1062</x:v>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="81" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="B93" s="81" t="str">
+        <x:v>Scale / sharding</x:v>
+      </x:c>
+      <x:c r="C93" s="82" t="str">
+        <x:v>Số shard</x:v>
+      </x:c>
+      <x:c r="D93" s="83" t="str">
+        <x:v>n_shard</x:v>
+      </x:c>
+      <x:c r="E93" s="84" t="str">
+        <x:v>Số shard parent thực sự đã chạy</x:v>
+      </x:c>
+      <x:c r="F93" s="84" t="str">
+        <x:v>Shard diagnostics</x:v>
+      </x:c>
+      <x:c r="G93" s="84" t="str">
+        <x:v>P10/P11</x:v>
+      </x:c>
+      <x:c r="H93" s="83" t="str">
+        <x:v>Bắt buộc</x:v>
+      </x:c>
+      <x:c r="I93" s="83" t="str">
+        <x:v>↓ với cùng giới hạn RAM</x:v>
+      </x:c>
+      <x:c r="J93" s="84" t="str">
+        <x:v>Phải đi kèm shard_rows_limit và quy tắc chia xác định.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="81" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="B94" s="81" t="str">
+        <x:v>Scale / sharding</x:v>
+      </x:c>
+      <x:c r="C94" s="82" t="str">
+        <x:v>Shard lớn nhất</x:v>
+      </x:c>
+      <x:c r="D94" s="83" t="str">
+        <x:v>N_shard,max</x:v>
+      </x:c>
+      <x:c r="E94" s="84" t="str">
+        <x:v>max số dòng trong một shard</x:v>
+      </x:c>
+      <x:c r="F94" s="84" t="str">
+        <x:v>Shard diagnostics</x:v>
+      </x:c>
+      <x:c r="G94" s="84" t="str">
+        <x:v>P10/P11</x:v>
+      </x:c>
+      <x:c r="H94" s="83" t="str">
+        <x:v>Bắt buộc</x:v>
+      </x:c>
+      <x:c r="I94" s="83" t="str">
+        <x:v>≤ giới hạn</x:v>
+      </x:c>
+      <x:c r="J94" s="84" t="str">
+        <x:v>Không thay cho peak RSS đo thực tế.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="81" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B95" s="81" t="str">
+        <x:v>Scale / sharding</x:v>
+      </x:c>
+      <x:c r="C95" s="82" t="str">
+        <x:v>Độ phủ train</x:v>
+      </x:c>
+      <x:c r="D95" s="83" t="str">
+        <x:v>Cov_train</x:v>
+      </x:c>
+      <x:c r="E95" s="84" t="str">
+        <x:v>train_rows_seen / N_train</x:v>
+      </x:c>
+      <x:c r="F95" s="84" t="str">
+        <x:v>all_train_rows_seen + row accounting</x:v>
+      </x:c>
+      <x:c r="G95" s="84" t="str">
+        <x:v>P10/P11</x:v>
+      </x:c>
+      <x:c r="H95" s="83" t="str">
+        <x:v>Bắt buộc</x:v>
+      </x:c>
+      <x:c r="I95" s="83" t="n">
+        <x:f>1</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J95" s="84" t="str">
+        <x:v>proxy_dataset phải=false; thiếu dòng là failure.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
